--- a/research/traditional_assets/database/data/thailand/thailand_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_beverage_alcoholic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09047399430661504</v>
+        <v>0.09032904631800182</v>
       </c>
       <c r="C2">
-        <v>17398.59846882383</v>
+        <v>17266.82357928388</v>
       </c>
       <c r="D2">
-        <v>15726.69846882383</v>
+        <v>15769.70757928388</v>
       </c>
       <c r="E2">
-        <v>-7443.9</v>
+        <v>-7269.116</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>174.784</v>
       </c>
       <c r="G2">
         <v>1671.9</v>
@@ -1457,28 +1457,28 @@
         <v>1354</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.7916352</v>
       </c>
       <c r="N2">
-        <v>1354</v>
+        <v>1345.2083648</v>
       </c>
       <c r="O2">
-        <v>270.8</v>
+        <v>269.04167296</v>
       </c>
       <c r="P2">
-        <v>1083.2</v>
+        <v>1076.16669184</v>
       </c>
       <c r="Q2">
-        <v>1330.3</v>
+        <v>1323.26669184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09047399430661504</v>
+        <v>0.09083499628080992</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905986</v>
+        <v>0.6966770696190075</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.0100298975099</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09032904631800182</v>
+        <v>0.09018409832938858</v>
       </c>
       <c r="C3">
-        <v>17266.82357928388</v>
+        <v>17135.28457602556</v>
       </c>
       <c r="D3">
-        <v>15769.70757928388</v>
+        <v>15812.95257602556</v>
       </c>
       <c r="E3">
-        <v>-7269.116</v>
+        <v>-7094.331999999999</v>
       </c>
       <c r="F3">
-        <v>174.784</v>
+        <v>349.568</v>
       </c>
       <c r="G3">
         <v>1671.9</v>
@@ -1539,28 +1539,28 @@
         <v>1354</v>
       </c>
       <c r="M3">
-        <v>8.7916352</v>
+        <v>17.5832704</v>
       </c>
       <c r="N3">
-        <v>1345.2083648</v>
+        <v>1336.4167296</v>
       </c>
       <c r="O3">
-        <v>269.04167296</v>
+        <v>267.28334592</v>
       </c>
       <c r="P3">
-        <v>1076.16669184</v>
+        <v>1069.13338368</v>
       </c>
       <c r="Q3">
-        <v>1323.26669184</v>
+        <v>1316.23338368</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09083499628080992</v>
+        <v>0.09120336564223325</v>
       </c>
       <c r="T3">
-        <v>0.6966770696190075</v>
+        <v>0.7023756264847308</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.0100298975099</v>
+        <v>77.00501494875493</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09018409832938858</v>
+        <v>0.09003915034077535</v>
       </c>
       <c r="C4">
-        <v>17135.28457602556</v>
+        <v>17003.98340498582</v>
       </c>
       <c r="D4">
-        <v>15812.95257602556</v>
+        <v>15856.43540498582</v>
       </c>
       <c r="E4">
-        <v>-7094.331999999999</v>
+        <v>-6919.548</v>
       </c>
       <c r="F4">
-        <v>349.568</v>
+        <v>524.352</v>
       </c>
       <c r="G4">
         <v>1671.9</v>
@@ -1621,28 +1621,28 @@
         <v>1354</v>
       </c>
       <c r="M4">
-        <v>17.5832704</v>
+        <v>26.3749056</v>
       </c>
       <c r="N4">
-        <v>1336.4167296</v>
+        <v>1327.6250944</v>
       </c>
       <c r="O4">
-        <v>267.28334592</v>
+        <v>265.52501888</v>
       </c>
       <c r="P4">
-        <v>1069.13338368</v>
+        <v>1062.10007552</v>
       </c>
       <c r="Q4">
-        <v>1316.23338368</v>
+        <v>1309.20007552</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09120336564223325</v>
+        <v>0.09157933024822201</v>
       </c>
       <c r="T4">
-        <v>0.7023756264847308</v>
+        <v>0.7081916793683041</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.00501494875493</v>
+        <v>51.33667663250329</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09003915034077535</v>
+        <v>0.08989420235216213</v>
       </c>
       <c r="C5">
-        <v>17003.98340498582</v>
+        <v>16872.92203356455</v>
       </c>
       <c r="D5">
-        <v>15856.43540498582</v>
+        <v>15900.15803356454</v>
       </c>
       <c r="E5">
-        <v>-6919.548</v>
+        <v>-6744.763999999999</v>
       </c>
       <c r="F5">
-        <v>524.352</v>
+        <v>699.1360000000001</v>
       </c>
       <c r="G5">
         <v>1671.9</v>
@@ -1703,28 +1703,28 @@
         <v>1354</v>
       </c>
       <c r="M5">
-        <v>26.3749056</v>
+        <v>35.1665408</v>
       </c>
       <c r="N5">
-        <v>1327.6250944</v>
+        <v>1318.8334592</v>
       </c>
       <c r="O5">
-        <v>265.52501888</v>
+        <v>263.76669184</v>
       </c>
       <c r="P5">
-        <v>1062.10007552</v>
+        <v>1055.06676736</v>
       </c>
       <c r="Q5">
-        <v>1309.20007552</v>
+        <v>1302.16676736</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09157933024822201</v>
+        <v>0.09196312745016888</v>
       </c>
       <c r="T5">
-        <v>0.7081916793683041</v>
+        <v>0.7141289000202853</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.33667663250329</v>
+        <v>38.50250747437747</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08989420235216213</v>
+        <v>0.08974925436354889</v>
       </c>
       <c r="C6">
-        <v>16872.92203356455</v>
+        <v>16742.10245092131</v>
       </c>
       <c r="D6">
-        <v>15900.15803356454</v>
+        <v>15944.12245092131</v>
       </c>
       <c r="E6">
-        <v>-6744.763999999999</v>
+        <v>-6569.98</v>
       </c>
       <c r="F6">
-        <v>699.1360000000001</v>
+        <v>873.9200000000001</v>
       </c>
       <c r="G6">
         <v>1671.9</v>
@@ -1785,28 +1785,28 @@
         <v>1354</v>
       </c>
       <c r="M6">
-        <v>35.1665408</v>
+        <v>43.958176</v>
       </c>
       <c r="N6">
-        <v>1318.8334592</v>
+        <v>1310.041824</v>
       </c>
       <c r="O6">
-        <v>263.76669184</v>
+        <v>262.0083648</v>
       </c>
       <c r="P6">
-        <v>1055.06676736</v>
+        <v>1048.0334592</v>
       </c>
       <c r="Q6">
-        <v>1302.16676736</v>
+        <v>1295.1334592</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09196312745016888</v>
+        <v>0.09235500459320936</v>
       </c>
       <c r="T6">
-        <v>0.7141289000202853</v>
+        <v>0.7201911147912553</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.50250747437747</v>
+        <v>30.80200597950197</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08974925436354889</v>
+        <v>0.08960430637493567</v>
       </c>
       <c r="C7">
-        <v>16742.10245092131</v>
+        <v>16611.52666827702</v>
       </c>
       <c r="D7">
-        <v>15944.12245092131</v>
+        <v>15988.33066827703</v>
       </c>
       <c r="E7">
-        <v>-6569.98</v>
+        <v>-6395.196</v>
       </c>
       <c r="F7">
-        <v>873.9200000000001</v>
+        <v>1048.704</v>
       </c>
       <c r="G7">
         <v>1671.9</v>
@@ -1867,28 +1867,28 @@
         <v>1354</v>
       </c>
       <c r="M7">
-        <v>43.958176</v>
+        <v>52.7498112</v>
       </c>
       <c r="N7">
-        <v>1310.041824</v>
+        <v>1301.2501888</v>
       </c>
       <c r="O7">
-        <v>262.0083648</v>
+        <v>260.25003776</v>
       </c>
       <c r="P7">
-        <v>1048.0334592</v>
+        <v>1041.00015104</v>
       </c>
       <c r="Q7">
-        <v>1295.1334592</v>
+        <v>1288.10015104</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09235500459320936</v>
+        <v>0.09275521954780391</v>
       </c>
       <c r="T7">
-        <v>0.7201911147912553</v>
+        <v>0.726382312855225</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.80200597950197</v>
+        <v>25.66833831625164</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08960430637493567</v>
+        <v>0.08945935838632245</v>
       </c>
       <c r="C8">
-        <v>16611.52666827702</v>
+        <v>16481.19671922065</v>
       </c>
       <c r="D8">
-        <v>15988.33066827703</v>
+        <v>16032.78471922065</v>
       </c>
       <c r="E8">
-        <v>-6395.196</v>
+        <v>-6220.411999999999</v>
       </c>
       <c r="F8">
-        <v>1048.704</v>
+        <v>1223.488</v>
       </c>
       <c r="G8">
         <v>1671.9</v>
@@ -1949,28 +1949,28 @@
         <v>1354</v>
       </c>
       <c r="M8">
-        <v>52.7498112</v>
+        <v>61.5414464</v>
       </c>
       <c r="N8">
-        <v>1301.2501888</v>
+        <v>1292.4585536</v>
       </c>
       <c r="O8">
-        <v>260.25003776</v>
+        <v>258.49171072</v>
       </c>
       <c r="P8">
-        <v>1041.00015104</v>
+        <v>1033.96684288</v>
       </c>
       <c r="Q8">
-        <v>1288.10015104</v>
+        <v>1281.06684288</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09275521954780391</v>
+        <v>0.09316404127561553</v>
       </c>
       <c r="T8">
-        <v>0.726382312855225</v>
+        <v>0.732706654963581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.66833831625164</v>
+        <v>22.00143284250141</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08945935838632244</v>
+        <v>0.08931441039770921</v>
       </c>
       <c r="C9">
-        <v>16481.19671922066</v>
+        <v>16351.11466002103</v>
       </c>
       <c r="D9">
-        <v>16032.78471922066</v>
+        <v>16077.48666002103</v>
       </c>
       <c r="E9">
-        <v>-6220.411999999999</v>
+        <v>-6045.628</v>
       </c>
       <c r="F9">
-        <v>1223.488</v>
+        <v>1398.272</v>
       </c>
       <c r="G9">
         <v>1671.9</v>
@@ -2031,28 +2031,28 @@
         <v>1354</v>
       </c>
       <c r="M9">
-        <v>61.54144640000001</v>
+        <v>70.3330816</v>
       </c>
       <c r="N9">
-        <v>1292.4585536</v>
+        <v>1283.6669184</v>
       </c>
       <c r="O9">
-        <v>258.49171072</v>
+        <v>256.73338368</v>
       </c>
       <c r="P9">
-        <v>1033.96684288</v>
+        <v>1026.93353472</v>
       </c>
       <c r="Q9">
-        <v>1281.06684288</v>
+        <v>1274.03353472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09316404127561553</v>
+        <v>0.09358175043229261</v>
       </c>
       <c r="T9">
-        <v>0.732706654963581</v>
+        <v>0.7391684827699446</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.0014328425014</v>
+        <v>19.25125373718873</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08931441039770921</v>
+        <v>0.08916946240909598</v>
       </c>
       <c r="C10">
-        <v>16351.11466002103</v>
+        <v>16221.28256994391</v>
       </c>
       <c r="D10">
-        <v>16077.48666002103</v>
+        <v>16122.43856994391</v>
       </c>
       <c r="E10">
-        <v>-6045.628</v>
+        <v>-5870.843999999999</v>
       </c>
       <c r="F10">
-        <v>1398.272</v>
+        <v>1573.056</v>
       </c>
       <c r="G10">
         <v>1671.9</v>
@@ -2113,28 +2113,28 @@
         <v>1354</v>
       </c>
       <c r="M10">
-        <v>70.3330816</v>
+        <v>79.1247168</v>
       </c>
       <c r="N10">
-        <v>1283.6669184</v>
+        <v>1274.8752832</v>
       </c>
       <c r="O10">
-        <v>256.73338368</v>
+        <v>254.97505664</v>
       </c>
       <c r="P10">
-        <v>1026.93353472</v>
+        <v>1019.90022656</v>
       </c>
       <c r="Q10">
-        <v>1274.03353472</v>
+        <v>1267.00022656</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09358175043229261</v>
+        <v>0.09400864000999558</v>
       </c>
       <c r="T10">
-        <v>0.7391684827699446</v>
+        <v>0.7457723287698548</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.25125373718873</v>
+        <v>17.11222554416776</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08916946240909598</v>
+        <v>0.08902451442048273</v>
       </c>
       <c r="C11">
-        <v>16221.28256994391</v>
+        <v>16091.70255157438</v>
       </c>
       <c r="D11">
-        <v>16122.43856994391</v>
+        <v>16167.64255157438</v>
       </c>
       <c r="E11">
-        <v>-5870.843999999999</v>
+        <v>-5696.059999999999</v>
       </c>
       <c r="F11">
-        <v>1573.056</v>
+        <v>1747.84</v>
       </c>
       <c r="G11">
         <v>1671.9</v>
@@ -2195,28 +2195,28 @@
         <v>1354</v>
       </c>
       <c r="M11">
-        <v>79.1247168</v>
+        <v>87.91635199999999</v>
       </c>
       <c r="N11">
-        <v>1274.8752832</v>
+        <v>1266.083648</v>
       </c>
       <c r="O11">
-        <v>254.97505664</v>
+        <v>253.2167296</v>
       </c>
       <c r="P11">
-        <v>1019.90022656</v>
+        <v>1012.8669184</v>
       </c>
       <c r="Q11">
-        <v>1267.00022656</v>
+        <v>1259.9669184</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09400864000999558</v>
+        <v>0.09444501602275859</v>
       </c>
       <c r="T11">
-        <v>0.7457723287698548</v>
+        <v>0.7525229269030962</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.11222554416776</v>
+        <v>15.40100298975099</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08902451442048276</v>
+        <v>0.08887956643186951</v>
       </c>
       <c r="C12">
-        <v>16091.70255157437</v>
+        <v>15962.37673114468</v>
       </c>
       <c r="D12">
-        <v>16167.64255157437</v>
+        <v>16213.10073114467</v>
       </c>
       <c r="E12">
-        <v>-5696.059999999999</v>
+        <v>-5521.276</v>
       </c>
       <c r="F12">
-        <v>1747.84</v>
+        <v>1922.624</v>
       </c>
       <c r="G12">
         <v>1671.9</v>
@@ -2277,28 +2277,28 @@
         <v>1354</v>
       </c>
       <c r="M12">
-        <v>87.916352</v>
+        <v>96.70798720000001</v>
       </c>
       <c r="N12">
-        <v>1266.083648</v>
+        <v>1257.2920128</v>
       </c>
       <c r="O12">
-        <v>253.2167296</v>
+        <v>251.45840256</v>
       </c>
       <c r="P12">
-        <v>1012.8669184</v>
+        <v>1005.83361024</v>
       </c>
       <c r="Q12">
-        <v>1259.9669184</v>
+        <v>1252.93361024</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09444501602275862</v>
+        <v>0.09489119823805563</v>
       </c>
       <c r="T12">
-        <v>0.7525229269030964</v>
+        <v>0.7594252238707926</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.40100298975099</v>
+        <v>14.00091180886453</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08887956643186951</v>
+        <v>0.08873461844325628</v>
       </c>
       <c r="C13">
-        <v>15962.37673114468</v>
+        <v>15833.30725886757</v>
       </c>
       <c r="D13">
-        <v>16213.10073114467</v>
+        <v>16258.81525886757</v>
       </c>
       <c r="E13">
-        <v>-5521.276</v>
+        <v>-5346.492</v>
       </c>
       <c r="F13">
-        <v>1922.624</v>
+        <v>2097.408</v>
       </c>
       <c r="G13">
         <v>1671.9</v>
@@ -2359,28 +2359,28 @@
         <v>1354</v>
       </c>
       <c r="M13">
-        <v>96.70798720000001</v>
+        <v>105.4996224</v>
       </c>
       <c r="N13">
-        <v>1257.2920128</v>
+        <v>1248.5003776</v>
       </c>
       <c r="O13">
-        <v>251.45840256</v>
+        <v>249.70007552</v>
       </c>
       <c r="P13">
-        <v>1005.83361024</v>
+        <v>998.8003020800001</v>
       </c>
       <c r="Q13">
-        <v>1252.93361024</v>
+        <v>1245.90030208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09489119823805563</v>
+        <v>0.09534752095824578</v>
       </c>
       <c r="T13">
-        <v>0.7594252238707926</v>
+        <v>0.7664843912241185</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.00091180886453</v>
+        <v>12.83416915812582</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08873461844325628</v>
+        <v>0.08858967045464305</v>
       </c>
       <c r="C14">
-        <v>15833.30725886757</v>
+        <v>15704.49630927541</v>
       </c>
       <c r="D14">
-        <v>16258.81525886757</v>
+        <v>16304.78830927541</v>
       </c>
       <c r="E14">
-        <v>-5346.492</v>
+        <v>-5171.707999999999</v>
       </c>
       <c r="F14">
-        <v>2097.408</v>
+        <v>2272.192</v>
       </c>
       <c r="G14">
         <v>1671.9</v>
@@ -2441,28 +2441,28 @@
         <v>1354</v>
       </c>
       <c r="M14">
-        <v>105.4996224</v>
+        <v>114.2912576</v>
       </c>
       <c r="N14">
-        <v>1248.5003776</v>
+        <v>1239.7087424</v>
       </c>
       <c r="O14">
-        <v>249.70007552</v>
+        <v>247.94174848</v>
       </c>
       <c r="P14">
-        <v>998.8003020800001</v>
+        <v>991.7669939199999</v>
       </c>
       <c r="Q14">
-        <v>1245.90030208</v>
+        <v>1238.86699392</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09534752095824578</v>
+        <v>0.09581433385591155</v>
       </c>
       <c r="T14">
-        <v>0.7664843912241185</v>
+        <v>0.7737058382867161</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.83416915812582</v>
+        <v>11.84692537673152</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08858967045464305</v>
+        <v>0.08844472246602983</v>
       </c>
       <c r="C15">
-        <v>15704.49630927541</v>
+        <v>15575.94608156491</v>
       </c>
       <c r="D15">
-        <v>16304.78830927541</v>
+        <v>16351.02208156491</v>
       </c>
       <c r="E15">
-        <v>-5171.707999999999</v>
+        <v>-4996.923999999999</v>
       </c>
       <c r="F15">
-        <v>2272.192</v>
+        <v>2446.976000000001</v>
       </c>
       <c r="G15">
         <v>1671.9</v>
@@ -2523,28 +2523,28 @@
         <v>1354</v>
       </c>
       <c r="M15">
-        <v>114.2912576</v>
+        <v>123.0828928</v>
       </c>
       <c r="N15">
-        <v>1239.7087424</v>
+        <v>1230.9171072</v>
       </c>
       <c r="O15">
-        <v>247.94174848</v>
+        <v>246.18342144</v>
       </c>
       <c r="P15">
-        <v>991.7669939199999</v>
+        <v>984.73368576</v>
       </c>
       <c r="Q15">
-        <v>1238.86699392</v>
+        <v>1231.83368576</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09581433385591155</v>
+        <v>0.09629200286747655</v>
       </c>
       <c r="T15">
-        <v>0.7737058382867161</v>
+        <v>0.7810952259786766</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.84692537673152</v>
+        <v>11.0007164212507</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08844472246602983</v>
+        <v>0.08829977447741659</v>
       </c>
       <c r="C16">
-        <v>15575.94608156491</v>
+        <v>15447.65879994784</v>
       </c>
       <c r="D16">
-        <v>16351.02208156491</v>
+        <v>16397.51879994784</v>
       </c>
       <c r="E16">
-        <v>-4996.923999999999</v>
+        <v>-4822.139999999999</v>
       </c>
       <c r="F16">
-        <v>2446.976000000001</v>
+        <v>2621.760000000001</v>
       </c>
       <c r="G16">
         <v>1671.9</v>
@@ -2605,28 +2605,28 @@
         <v>1354</v>
       </c>
       <c r="M16">
-        <v>123.0828928</v>
+        <v>131.874528</v>
       </c>
       <c r="N16">
-        <v>1230.9171072</v>
+        <v>1222.125472</v>
       </c>
       <c r="O16">
-        <v>246.18342144</v>
+        <v>244.4250944</v>
       </c>
       <c r="P16">
-        <v>984.73368576</v>
+        <v>977.7003775999999</v>
       </c>
       <c r="Q16">
-        <v>1231.83368576</v>
+        <v>1224.8003776</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09629200286747655</v>
+        <v>0.09678091114990187</v>
       </c>
       <c r="T16">
-        <v>0.7810952259786766</v>
+        <v>0.7886584816163301</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.0007164212507</v>
+        <v>10.26733532650066</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08829977447741659</v>
+        <v>0.08815482648880335</v>
       </c>
       <c r="C17">
-        <v>15447.65879994784</v>
+        <v>15319.6367140077</v>
       </c>
       <c r="D17">
-        <v>16397.51879994784</v>
+        <v>16444.2807140077</v>
       </c>
       <c r="E17">
-        <v>-4822.139999999999</v>
+        <v>-4647.356</v>
       </c>
       <c r="F17">
-        <v>2621.76</v>
+        <v>2796.544</v>
       </c>
       <c r="G17">
         <v>1671.9</v>
@@ -2687,28 +2687,28 @@
         <v>1354</v>
       </c>
       <c r="M17">
-        <v>131.874528</v>
+        <v>140.6661632</v>
       </c>
       <c r="N17">
-        <v>1222.125472</v>
+        <v>1213.3338368</v>
       </c>
       <c r="O17">
-        <v>244.4250944</v>
+        <v>242.66676736</v>
       </c>
       <c r="P17">
-        <v>977.7003775999999</v>
+        <v>970.66706944</v>
       </c>
       <c r="Q17">
-        <v>1224.8003776</v>
+        <v>1217.76706944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09678091114990187</v>
+        <v>0.09728146010571828</v>
       </c>
       <c r="T17">
-        <v>0.7886584816163301</v>
+        <v>0.7964018147691659</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.26733532650066</v>
+        <v>9.625626868594365</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08815482648880335</v>
+        <v>0.08800987850019013</v>
       </c>
       <c r="C18">
-        <v>15319.6367140077</v>
+        <v>15191.88209906255</v>
       </c>
       <c r="D18">
-        <v>16444.2807140077</v>
+        <v>16491.31009906255</v>
       </c>
       <c r="E18">
-        <v>-4647.356</v>
+        <v>-4472.571999999999</v>
       </c>
       <c r="F18">
-        <v>2796.544</v>
+        <v>2971.328</v>
       </c>
       <c r="G18">
         <v>1671.9</v>
@@ -2769,28 +2769,28 @@
         <v>1354</v>
       </c>
       <c r="M18">
-        <v>140.6661632</v>
+        <v>149.4577984</v>
       </c>
       <c r="N18">
-        <v>1213.3338368</v>
+        <v>1204.5422016</v>
       </c>
       <c r="O18">
-        <v>242.66676736</v>
+        <v>240.90844032</v>
       </c>
       <c r="P18">
-        <v>970.66706944</v>
+        <v>963.63376128</v>
       </c>
       <c r="Q18">
-        <v>1217.76706944</v>
+        <v>1210.73376128</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09728146010571828</v>
+        <v>0.09779407048215678</v>
       </c>
       <c r="T18">
-        <v>0.7964018147691659</v>
+        <v>0.8043317342630341</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.625626868594365</v>
+        <v>9.059413523382933</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08800987850019013</v>
+        <v>0.08808093051157689</v>
       </c>
       <c r="C19">
-        <v>15191.88209906255</v>
+        <v>14994.011213692</v>
       </c>
       <c r="D19">
-        <v>16491.31009906255</v>
+        <v>16468.223213692</v>
       </c>
       <c r="E19">
-        <v>-4472.571999999999</v>
+        <v>-4297.787999999999</v>
       </c>
       <c r="F19">
-        <v>2971.328</v>
+        <v>3146.112000000001</v>
       </c>
       <c r="G19">
         <v>1671.9</v>
@@ -2851,45 +2851,45 @@
         <v>1354</v>
       </c>
       <c r="M19">
-        <v>149.4577984</v>
+        <v>162.9686016</v>
       </c>
       <c r="N19">
-        <v>1204.5422016</v>
+        <v>1191.0313984</v>
       </c>
       <c r="O19">
-        <v>240.90844032</v>
+        <v>238.20627968</v>
       </c>
       <c r="P19">
-        <v>963.63376128</v>
+        <v>952.82511872</v>
       </c>
       <c r="Q19">
-        <v>1210.73376128</v>
+        <v>1199.92511872</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09779407048215678</v>
+        <v>0.09831918355070354</v>
       </c>
       <c r="T19">
-        <v>0.8043317342630341</v>
+        <v>0.8124550664274843</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.059413523382933</v>
+        <v>8.308348888722378</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08808093051157691</v>
+        <v>0.08794798252296368</v>
       </c>
       <c r="C20">
-        <v>14994.01121369199</v>
+        <v>14862.47874094869</v>
       </c>
       <c r="D20">
-        <v>16468.22321369199</v>
+        <v>16511.47474094868</v>
       </c>
       <c r="E20">
-        <v>-4297.788</v>
+        <v>-4123.003999999999</v>
       </c>
       <c r="F20">
-        <v>3146.112</v>
+        <v>3320.896</v>
       </c>
       <c r="G20">
         <v>1671.9</v>
@@ -2933,28 +2933,28 @@
         <v>1354</v>
       </c>
       <c r="M20">
-        <v>162.9686016</v>
+        <v>172.0224128</v>
       </c>
       <c r="N20">
-        <v>1191.0313984</v>
+        <v>1181.9775872</v>
       </c>
       <c r="O20">
-        <v>238.20627968</v>
+        <v>236.39551744</v>
       </c>
       <c r="P20">
-        <v>952.82511872</v>
+        <v>945.58206976</v>
       </c>
       <c r="Q20">
-        <v>1199.92511872</v>
+        <v>1192.68206976</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09831918355070354</v>
+        <v>0.09885726237402923</v>
       </c>
       <c r="T20">
-        <v>0.8124550664274842</v>
+        <v>0.8207789746947605</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.308348888722378</v>
+        <v>7.871067368263305</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08794798252296368</v>
+        <v>0.08781503453435045</v>
       </c>
       <c r="C21">
-        <v>14862.47874094869</v>
+        <v>14731.17405485193</v>
       </c>
       <c r="D21">
-        <v>16511.47474094868</v>
+        <v>16554.95405485193</v>
       </c>
       <c r="E21">
-        <v>-4123.003999999999</v>
+        <v>-3948.219999999999</v>
       </c>
       <c r="F21">
-        <v>3320.896</v>
+        <v>3495.68</v>
       </c>
       <c r="G21">
         <v>1671.9</v>
@@ -3015,28 +3015,28 @@
         <v>1354</v>
       </c>
       <c r="M21">
-        <v>172.0224128</v>
+        <v>181.076224</v>
       </c>
       <c r="N21">
-        <v>1181.9775872</v>
+        <v>1172.923776</v>
       </c>
       <c r="O21">
-        <v>236.39551744</v>
+        <v>234.5847552</v>
       </c>
       <c r="P21">
-        <v>945.58206976</v>
+        <v>938.3390208000001</v>
       </c>
       <c r="Q21">
-        <v>1192.68206976</v>
+        <v>1185.4390208</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09885726237402923</v>
+        <v>0.09940879316793805</v>
       </c>
       <c r="T21">
-        <v>0.8207789746947605</v>
+        <v>0.8293109806687183</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.871067368263305</v>
+        <v>7.47751399985014</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08781503453435045</v>
+        <v>0.08768208654573721</v>
       </c>
       <c r="C22">
-        <v>14731.17405485193</v>
+        <v>14600.0989596299</v>
       </c>
       <c r="D22">
-        <v>16554.95405485193</v>
+        <v>16598.6629596299</v>
       </c>
       <c r="E22">
-        <v>-3948.219999999999</v>
+        <v>-3773.435999999999</v>
       </c>
       <c r="F22">
-        <v>3495.68</v>
+        <v>3670.464000000001</v>
       </c>
       <c r="G22">
         <v>1671.9</v>
@@ -3097,28 +3097,28 @@
         <v>1354</v>
       </c>
       <c r="M22">
-        <v>181.076224</v>
+        <v>190.1300352</v>
       </c>
       <c r="N22">
-        <v>1172.923776</v>
+        <v>1163.8699648</v>
       </c>
       <c r="O22">
-        <v>234.5847552</v>
+        <v>232.77399296</v>
       </c>
       <c r="P22">
-        <v>938.3390208000001</v>
+        <v>931.0959718399999</v>
       </c>
       <c r="Q22">
-        <v>1185.4390208</v>
+        <v>1178.19597184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09940879316793805</v>
+        <v>0.09997428676675596</v>
       </c>
       <c r="T22">
-        <v>0.8293109806687183</v>
+        <v>0.8380589867939158</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.47751399985014</v>
+        <v>7.121441904619179</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08768208654573721</v>
+        <v>0.08754913855712398</v>
       </c>
       <c r="C23">
-        <v>14600.0989596299</v>
+        <v>14469.25527861551</v>
       </c>
       <c r="D23">
-        <v>16598.6629596299</v>
+        <v>16642.60327861551</v>
       </c>
       <c r="E23">
-        <v>-3773.435999999999</v>
+        <v>-3598.651999999999</v>
       </c>
       <c r="F23">
-        <v>3670.464</v>
+        <v>3845.248000000001</v>
       </c>
       <c r="G23">
         <v>1671.9</v>
@@ -3179,28 +3179,28 @@
         <v>1354</v>
       </c>
       <c r="M23">
-        <v>190.1300352</v>
+        <v>199.1838464</v>
       </c>
       <c r="N23">
-        <v>1163.8699648</v>
+        <v>1154.8161536</v>
       </c>
       <c r="O23">
-        <v>232.77399296</v>
+        <v>230.96323072</v>
       </c>
       <c r="P23">
-        <v>931.0959718399999</v>
+        <v>923.8529228800001</v>
       </c>
       <c r="Q23">
-        <v>1178.19597184</v>
+        <v>1170.95292288</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09997428676675596</v>
+        <v>0.100554280201441</v>
       </c>
       <c r="T23">
-        <v>0.8380589867939158</v>
+        <v>0.8470313007684773</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.12144190461918</v>
+        <v>6.797739999863763</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08754913855712398</v>
+        <v>0.08772899056851076</v>
       </c>
       <c r="C24">
-        <v>14469.25527861551</v>
+        <v>14235.08414173069</v>
       </c>
       <c r="D24">
-        <v>16642.60327861551</v>
+        <v>16583.21614173069</v>
       </c>
       <c r="E24">
-        <v>-3598.651999999999</v>
+        <v>-3423.867999999999</v>
       </c>
       <c r="F24">
-        <v>3845.248000000001</v>
+        <v>4020.032000000001</v>
       </c>
       <c r="G24">
         <v>1671.9</v>
@@ -3261,45 +3261,45 @@
         <v>1354</v>
       </c>
       <c r="M24">
-        <v>199.1838464</v>
+        <v>215.071712</v>
       </c>
       <c r="N24">
-        <v>1154.8161536</v>
+        <v>1138.928288</v>
       </c>
       <c r="O24">
-        <v>230.96323072</v>
+        <v>227.7856576</v>
       </c>
       <c r="P24">
-        <v>923.8529228800001</v>
+        <v>911.1426304</v>
       </c>
       <c r="Q24">
-        <v>1170.95292288</v>
+        <v>1158.2426304</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.100554280201441</v>
+        <v>0.1011493384006633</v>
       </c>
       <c r="T24">
-        <v>0.8470313007684773</v>
+        <v>0.8562366618592612</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.797739999863763</v>
+        <v>6.295574566310236</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08772899056851076</v>
+        <v>0.08760964257989753</v>
       </c>
       <c r="C25">
-        <v>14235.08414173069</v>
+        <v>14099.66142934343</v>
       </c>
       <c r="D25">
-        <v>16583.21614173069</v>
+        <v>16622.57742934343</v>
       </c>
       <c r="E25">
-        <v>-3423.867999999999</v>
+        <v>-3249.083999999999</v>
       </c>
       <c r="F25">
-        <v>4020.032000000001</v>
+        <v>4194.816000000001</v>
       </c>
       <c r="G25">
         <v>1671.9</v>
@@ -3343,28 +3343,28 @@
         <v>1354</v>
       </c>
       <c r="M25">
-        <v>215.071712</v>
+        <v>224.422656</v>
       </c>
       <c r="N25">
-        <v>1138.928288</v>
+        <v>1129.577344</v>
       </c>
       <c r="O25">
-        <v>227.7856576</v>
+        <v>225.9154688</v>
       </c>
       <c r="P25">
-        <v>911.1426304</v>
+        <v>903.6618752000001</v>
       </c>
       <c r="Q25">
-        <v>1158.2426304</v>
+        <v>1150.7618752</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1011493384006633</v>
+        <v>0.101760056026181</v>
       </c>
       <c r="T25">
-        <v>0.8562366618592612</v>
+        <v>0.8656842692945395</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.295574566310236</v>
+        <v>6.033258959380642</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08760964257989752</v>
+        <v>0.0874902945912843</v>
       </c>
       <c r="C26">
-        <v>14099.66142934344</v>
+        <v>13964.42601441208</v>
       </c>
       <c r="D26">
-        <v>16622.57742934344</v>
+        <v>16662.12601441208</v>
       </c>
       <c r="E26">
-        <v>-3249.084</v>
+        <v>-3074.299999999999</v>
       </c>
       <c r="F26">
-        <v>4194.816</v>
+        <v>4369.6</v>
       </c>
       <c r="G26">
         <v>1671.9</v>
@@ -3425,28 +3425,28 @@
         <v>1354</v>
       </c>
       <c r="M26">
-        <v>224.422656</v>
+        <v>233.7736</v>
       </c>
       <c r="N26">
-        <v>1129.577344</v>
+        <v>1120.2264</v>
       </c>
       <c r="O26">
-        <v>225.9154688</v>
+        <v>224.04528</v>
       </c>
       <c r="P26">
-        <v>903.6618752000001</v>
+        <v>896.18112</v>
       </c>
       <c r="Q26">
-        <v>1150.7618752</v>
+        <v>1143.28112</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1017600560261809</v>
+        <v>0.1023870594550457</v>
       </c>
       <c r="T26">
-        <v>0.8656842692945392</v>
+        <v>0.8753838129280915</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.033258959380643</v>
+        <v>5.791928601005417</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0874902945912843</v>
+        <v>0.08753734660267105</v>
       </c>
       <c r="C27">
-        <v>13964.42601441208</v>
+        <v>13774.02784384946</v>
       </c>
       <c r="D27">
-        <v>16662.12601441208</v>
+        <v>16646.51184384946</v>
       </c>
       <c r="E27">
-        <v>-3074.299999999999</v>
+        <v>-2899.515999999999</v>
       </c>
       <c r="F27">
-        <v>4369.6</v>
+        <v>4544.384000000001</v>
       </c>
       <c r="G27">
         <v>1671.9</v>
@@ -3507,45 +3507,45 @@
         <v>1354</v>
       </c>
       <c r="M27">
-        <v>233.7736</v>
+        <v>246.7600512</v>
       </c>
       <c r="N27">
-        <v>1120.2264</v>
+        <v>1107.2399488</v>
       </c>
       <c r="O27">
-        <v>224.04528</v>
+        <v>221.44798976</v>
       </c>
       <c r="P27">
-        <v>896.18112</v>
+        <v>885.7919590399999</v>
       </c>
       <c r="Q27">
-        <v>1143.28112</v>
+        <v>1132.89195904</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1023870594550457</v>
+        <v>0.1030310089225285</v>
       </c>
       <c r="T27">
-        <v>0.8753838129280915</v>
+        <v>0.8853455063895778</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.791928601005417</v>
+        <v>5.487111845760549</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08753734660267105</v>
+        <v>0.08742439861405783</v>
       </c>
       <c r="C28">
-        <v>13774.02784384946</v>
+        <v>13636.77484147481</v>
       </c>
       <c r="D28">
-        <v>16646.51184384946</v>
+        <v>16684.04284147481</v>
       </c>
       <c r="E28">
-        <v>-2899.515999999999</v>
+        <v>-2724.731999999999</v>
       </c>
       <c r="F28">
-        <v>4544.384000000001</v>
+        <v>4719.168000000001</v>
       </c>
       <c r="G28">
         <v>1671.9</v>
@@ -3589,28 +3589,28 @@
         <v>1354</v>
       </c>
       <c r="M28">
-        <v>246.7600512</v>
+        <v>256.2508224000001</v>
       </c>
       <c r="N28">
-        <v>1107.2399488</v>
+        <v>1097.7491776</v>
       </c>
       <c r="O28">
-        <v>221.44798976</v>
+        <v>219.54983552</v>
       </c>
       <c r="P28">
-        <v>885.7919590399999</v>
+        <v>878.19934208</v>
       </c>
       <c r="Q28">
-        <v>1132.89195904</v>
+        <v>1125.29934208</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1030310089225285</v>
+        <v>0.1036926008411751</v>
       </c>
       <c r="T28">
-        <v>0.8853455063895778</v>
+        <v>0.8955801229595978</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.487111845760549</v>
+        <v>5.283885481102751</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08742439861405783</v>
+        <v>0.0873114506254446</v>
       </c>
       <c r="C29">
-        <v>13636.77484147481</v>
+        <v>13499.69145526093</v>
       </c>
       <c r="D29">
-        <v>16684.04284147481</v>
+        <v>16721.74345526093</v>
       </c>
       <c r="E29">
-        <v>-2724.731999999999</v>
+        <v>-2549.947999999999</v>
       </c>
       <c r="F29">
-        <v>4719.168000000001</v>
+        <v>4893.952000000001</v>
       </c>
       <c r="G29">
         <v>1671.9</v>
@@ -3671,28 +3671,28 @@
         <v>1354</v>
       </c>
       <c r="M29">
-        <v>256.2508224000001</v>
+        <v>265.7415936</v>
       </c>
       <c r="N29">
-        <v>1097.7491776</v>
+        <v>1088.2584064</v>
       </c>
       <c r="O29">
-        <v>219.54983552</v>
+        <v>217.65168128</v>
       </c>
       <c r="P29">
-        <v>878.19934208</v>
+        <v>870.60672512</v>
       </c>
       <c r="Q29">
-        <v>1125.29934208</v>
+        <v>1117.70672512</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1036926008411751</v>
+        <v>0.1043725703131175</v>
       </c>
       <c r="T29">
-        <v>0.8955801229595978</v>
+        <v>0.9060990344343405</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.283885481102751</v>
+        <v>5.095175285349082</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0873114506254446</v>
+        <v>0.08719850263683138</v>
       </c>
       <c r="C30">
-        <v>13499.69145526093</v>
+        <v>13362.7788376472</v>
       </c>
       <c r="D30">
-        <v>16721.74345526093</v>
+        <v>16759.6148376472</v>
       </c>
       <c r="E30">
-        <v>-2549.947999999999</v>
+        <v>-2375.163999999999</v>
       </c>
       <c r="F30">
-        <v>4893.952000000001</v>
+        <v>5068.736000000001</v>
       </c>
       <c r="G30">
         <v>1671.9</v>
@@ -3753,28 +3753,28 @@
         <v>1354</v>
       </c>
       <c r="M30">
-        <v>265.7415936</v>
+        <v>275.2323648</v>
       </c>
       <c r="N30">
-        <v>1088.2584064</v>
+        <v>1078.7676352</v>
       </c>
       <c r="O30">
-        <v>217.65168128</v>
+        <v>215.75352704</v>
       </c>
       <c r="P30">
-        <v>870.60672512</v>
+        <v>863.0141081599999</v>
       </c>
       <c r="Q30">
-        <v>1117.70672512</v>
+        <v>1110.11410816</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1043725703131175</v>
+        <v>0.1050716938546921</v>
       </c>
       <c r="T30">
-        <v>0.9060990344343405</v>
+        <v>0.9169142532745689</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.095175285349082</v>
+        <v>4.919479585854286</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08719850263683138</v>
+        <v>0.08708555464821814</v>
       </c>
       <c r="C31">
-        <v>13362.7788376472</v>
+        <v>13226.03815153685</v>
       </c>
       <c r="D31">
-        <v>16759.6148376472</v>
+        <v>16797.65815153685</v>
       </c>
       <c r="E31">
-        <v>-2375.164</v>
+        <v>-2200.379999999999</v>
       </c>
       <c r="F31">
-        <v>5068.736</v>
+        <v>5243.52</v>
       </c>
       <c r="G31">
         <v>1671.9</v>
@@ -3835,28 +3835,28 @@
         <v>1354</v>
       </c>
       <c r="M31">
-        <v>275.2323648</v>
+        <v>284.723136</v>
       </c>
       <c r="N31">
-        <v>1078.7676352</v>
+        <v>1069.276864</v>
       </c>
       <c r="O31">
-        <v>215.75352704</v>
+        <v>213.8553728</v>
       </c>
       <c r="P31">
-        <v>863.0141081600001</v>
+        <v>855.4214912</v>
       </c>
       <c r="Q31">
-        <v>1110.11410816</v>
+        <v>1102.5214912</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1050716938546921</v>
+        <v>0.1057907923545973</v>
       </c>
       <c r="T31">
-        <v>0.9169142532745689</v>
+        <v>0.9280384783673754</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.919479585854288</v>
+        <v>4.755496932992477</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08708555464821814</v>
+        <v>0.08697260665960491</v>
       </c>
       <c r="C32">
-        <v>13226.03815153685</v>
+        <v>13089.47057041602</v>
       </c>
       <c r="D32">
-        <v>16797.65815153685</v>
+        <v>16835.87457041602</v>
       </c>
       <c r="E32">
-        <v>-2200.379999999999</v>
+        <v>-2025.596</v>
       </c>
       <c r="F32">
-        <v>5243.52</v>
+        <v>5418.304</v>
       </c>
       <c r="G32">
         <v>1671.9</v>
@@ -3917,28 +3917,28 @@
         <v>1354</v>
       </c>
       <c r="M32">
-        <v>284.723136</v>
+        <v>294.2139072</v>
       </c>
       <c r="N32">
-        <v>1069.276864</v>
+        <v>1059.7860928</v>
       </c>
       <c r="O32">
-        <v>213.8553728</v>
+        <v>211.95721856</v>
       </c>
       <c r="P32">
-        <v>855.4214912</v>
+        <v>847.82887424</v>
       </c>
       <c r="Q32">
-        <v>1102.5214912</v>
+        <v>1094.92887424</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1057907923545973</v>
+        <v>0.1065307342892825</v>
       </c>
       <c r="T32">
-        <v>0.9280384783673754</v>
+        <v>0.9394851447672196</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.755496932992477</v>
+        <v>4.602093806121752</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08697260665960491</v>
+        <v>0.08685965867099169</v>
       </c>
       <c r="C33">
-        <v>13089.47057041602</v>
+        <v>12953.07727847441</v>
       </c>
       <c r="D33">
-        <v>16835.87457041602</v>
+        <v>16874.26527847441</v>
       </c>
       <c r="E33">
-        <v>-2025.596</v>
+        <v>-1850.811999999999</v>
       </c>
       <c r="F33">
-        <v>5418.304</v>
+        <v>5593.088000000001</v>
       </c>
       <c r="G33">
         <v>1671.9</v>
@@ -3999,28 +3999,28 @@
         <v>1354</v>
       </c>
       <c r="M33">
-        <v>294.2139072</v>
+        <v>303.7046784</v>
       </c>
       <c r="N33">
-        <v>1059.7860928</v>
+        <v>1050.2953216</v>
       </c>
       <c r="O33">
-        <v>211.95721856</v>
+        <v>210.05906432</v>
       </c>
       <c r="P33">
-        <v>847.82887424</v>
+        <v>840.23625728</v>
       </c>
       <c r="Q33">
-        <v>1094.92887424</v>
+        <v>1087.33625728</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1065307342892825</v>
+        <v>0.1072924392220466</v>
       </c>
       <c r="T33">
-        <v>0.9394851447672196</v>
+        <v>0.9512684778258829</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.602093806121752</v>
+        <v>4.458278374680448</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08685965867099169</v>
+        <v>0.08674671068237845</v>
       </c>
       <c r="C34">
-        <v>12953.07727847441</v>
+        <v>12816.85947072762</v>
       </c>
       <c r="D34">
-        <v>16874.26527847441</v>
+        <v>16912.83147072762</v>
       </c>
       <c r="E34">
-        <v>-1850.811999999999</v>
+        <v>-1676.027999999999</v>
       </c>
       <c r="F34">
-        <v>5593.088000000001</v>
+        <v>5767.872</v>
       </c>
       <c r="G34">
         <v>1671.9</v>
@@ -4081,28 +4081,28 @@
         <v>1354</v>
       </c>
       <c r="M34">
-        <v>303.7046784</v>
+        <v>313.1954496</v>
       </c>
       <c r="N34">
-        <v>1050.2953216</v>
+        <v>1040.8045504</v>
       </c>
       <c r="O34">
-        <v>210.05906432</v>
+        <v>208.16091008</v>
       </c>
       <c r="P34">
-        <v>840.23625728</v>
+        <v>832.6436403199999</v>
       </c>
       <c r="Q34">
-        <v>1087.33625728</v>
+        <v>1079.74364032</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1072924392220466</v>
+        <v>0.1080768816154902</v>
       </c>
       <c r="T34">
-        <v>0.9512684778258829</v>
+        <v>0.9634035521698794</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.458278374680448</v>
+        <v>4.323179029993161</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08674671068237845</v>
+        <v>0.08690576269376522</v>
       </c>
       <c r="C35">
-        <v>12816.85947072762</v>
+        <v>12587.81752109711</v>
       </c>
       <c r="D35">
-        <v>16912.83147072762</v>
+        <v>16858.57352109711</v>
       </c>
       <c r="E35">
-        <v>-1676.027999999999</v>
+        <v>-1501.243999999999</v>
       </c>
       <c r="F35">
-        <v>5767.872</v>
+        <v>5942.656000000001</v>
       </c>
       <c r="G35">
         <v>1671.9</v>
@@ -4163,45 +4163,45 @@
         <v>1354</v>
       </c>
       <c r="M35">
-        <v>313.1954496</v>
+        <v>328.6288768000001</v>
       </c>
       <c r="N35">
-        <v>1040.8045504</v>
+        <v>1025.3711232</v>
       </c>
       <c r="O35">
-        <v>208.16091008</v>
+        <v>205.07422464</v>
       </c>
       <c r="P35">
-        <v>832.6436403199999</v>
+        <v>820.29689856</v>
       </c>
       <c r="Q35">
-        <v>1079.74364032</v>
+        <v>1067.39689856</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1080768816154902</v>
+        <v>0.1088850949905534</v>
       </c>
       <c r="T35">
-        <v>0.9634035521698794</v>
+        <v>0.9759063560394514</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.323179029993161</v>
+        <v>4.120149188301641</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08690576269376522</v>
+        <v>0.08680081470515198</v>
       </c>
       <c r="C36">
-        <v>12587.81752109711</v>
+        <v>12448.79563058339</v>
       </c>
       <c r="D36">
-        <v>16858.57352109711</v>
+        <v>16894.33563058339</v>
       </c>
       <c r="E36">
-        <v>-1501.243999999999</v>
+        <v>-1326.459999999998</v>
       </c>
       <c r="F36">
-        <v>5942.656000000001</v>
+        <v>6117.440000000001</v>
       </c>
       <c r="G36">
         <v>1671.9</v>
@@ -4245,28 +4245,28 @@
         <v>1354</v>
       </c>
       <c r="M36">
-        <v>328.6288768000001</v>
+        <v>338.2944320000001</v>
       </c>
       <c r="N36">
-        <v>1025.3711232</v>
+        <v>1015.705568</v>
       </c>
       <c r="O36">
-        <v>205.07422464</v>
+        <v>203.1411136</v>
       </c>
       <c r="P36">
-        <v>820.29689856</v>
+        <v>812.5644543999999</v>
       </c>
       <c r="Q36">
-        <v>1067.39689856</v>
+        <v>1059.6644544</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1088850949905534</v>
+        <v>0.1097181764694646</v>
       </c>
       <c r="T36">
-        <v>0.9759063560394514</v>
+        <v>0.9887938615665488</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.120149188301641</v>
+        <v>4.00243064006445</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08680081470515198</v>
+        <v>0.08669586671653877</v>
       </c>
       <c r="C37">
-        <v>12448.79563058339</v>
+        <v>12309.92578700683</v>
       </c>
       <c r="D37">
-        <v>16894.33563058339</v>
+        <v>16930.24978700683</v>
       </c>
       <c r="E37">
-        <v>-1326.459999999998</v>
+        <v>-1151.675999999999</v>
       </c>
       <c r="F37">
-        <v>6117.440000000001</v>
+        <v>6292.224000000001</v>
       </c>
       <c r="G37">
         <v>1671.9</v>
@@ -4327,28 +4327,28 @@
         <v>1354</v>
       </c>
       <c r="M37">
-        <v>338.2944320000001</v>
+        <v>347.9599872000001</v>
       </c>
       <c r="N37">
-        <v>1015.705568</v>
+        <v>1006.0400128</v>
       </c>
       <c r="O37">
-        <v>203.1411136</v>
+        <v>201.20800256</v>
       </c>
       <c r="P37">
-        <v>812.5644543999999</v>
+        <v>804.8320102399999</v>
       </c>
       <c r="Q37">
-        <v>1059.6644544</v>
+        <v>1051.93201024</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1097181764694646</v>
+        <v>0.1105772917445918</v>
       </c>
       <c r="T37">
-        <v>0.9887938615665488</v>
+        <v>1.002084101641368</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.00243064006445</v>
+        <v>3.891252011173771</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08669586671653876</v>
+        <v>0.08659091872792554</v>
       </c>
       <c r="C38">
-        <v>12309.92578700683</v>
+        <v>12171.20896210211</v>
       </c>
       <c r="D38">
-        <v>16930.24978700683</v>
+        <v>16966.31696210211</v>
       </c>
       <c r="E38">
-        <v>-1151.675999999999</v>
+        <v>-976.8919999999989</v>
       </c>
       <c r="F38">
-        <v>6292.224</v>
+        <v>6467.008000000001</v>
       </c>
       <c r="G38">
         <v>1671.9</v>
@@ -4409,28 +4409,28 @@
         <v>1354</v>
       </c>
       <c r="M38">
-        <v>347.9599872</v>
+        <v>357.6255424</v>
       </c>
       <c r="N38">
-        <v>1006.0400128</v>
+        <v>996.3744575999999</v>
       </c>
       <c r="O38">
-        <v>201.20800256</v>
+        <v>199.27489152</v>
       </c>
       <c r="P38">
-        <v>804.83201024</v>
+        <v>797.0995660799999</v>
       </c>
       <c r="Q38">
-        <v>1051.93201024</v>
+        <v>1044.19956608</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1105772917445918</v>
+        <v>0.1114636805205167</v>
       </c>
       <c r="T38">
-        <v>1.002084101641368</v>
+        <v>1.015796254099515</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.891252011173772</v>
+        <v>3.786083037898805</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08659091872792554</v>
+        <v>0.08648597073931229</v>
       </c>
       <c r="C39">
-        <v>12171.20896210211</v>
+        <v>12032.64613590208</v>
       </c>
       <c r="D39">
-        <v>16966.31696210211</v>
+        <v>17002.53813590208</v>
       </c>
       <c r="E39">
-        <v>-976.8919999999989</v>
+        <v>-802.1079999999993</v>
       </c>
       <c r="F39">
-        <v>6467.008000000001</v>
+        <v>6641.792</v>
       </c>
       <c r="G39">
         <v>1671.9</v>
@@ -4491,28 +4491,28 @@
         <v>1354</v>
       </c>
       <c r="M39">
-        <v>357.6255424</v>
+        <v>367.2910976000001</v>
       </c>
       <c r="N39">
-        <v>996.3744575999999</v>
+        <v>986.7089023999999</v>
       </c>
       <c r="O39">
-        <v>199.27489152</v>
+        <v>197.34178048</v>
       </c>
       <c r="P39">
-        <v>797.0995660799999</v>
+        <v>789.3671219199999</v>
       </c>
       <c r="Q39">
-        <v>1044.19956608</v>
+        <v>1036.46712192</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1114636805205167</v>
+        <v>0.1123786624827618</v>
       </c>
       <c r="T39">
-        <v>1.015796254099515</v>
+        <v>1.029950734056311</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.786083037898805</v>
+        <v>3.686449273743573</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08648597073931229</v>
+        <v>0.08638102275069906</v>
       </c>
       <c r="C40">
-        <v>12032.64613590208</v>
+        <v>11894.23829682648</v>
       </c>
       <c r="D40">
-        <v>17002.53813590208</v>
+        <v>17038.91429682648</v>
       </c>
       <c r="E40">
-        <v>-802.1079999999993</v>
+        <v>-627.3239999999987</v>
       </c>
       <c r="F40">
-        <v>6641.792</v>
+        <v>6816.576000000001</v>
       </c>
       <c r="G40">
         <v>1671.9</v>
@@ -4573,28 +4573,28 @@
         <v>1354</v>
       </c>
       <c r="M40">
-        <v>367.2910976000001</v>
+        <v>376.9566528000001</v>
       </c>
       <c r="N40">
-        <v>986.7089023999999</v>
+        <v>977.0433472</v>
       </c>
       <c r="O40">
-        <v>197.34178048</v>
+        <v>195.40866944</v>
       </c>
       <c r="P40">
-        <v>789.3671219199999</v>
+        <v>781.6346777599999</v>
       </c>
       <c r="Q40">
-        <v>1036.46712192</v>
+        <v>1028.73467776</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1123786624827618</v>
+        <v>0.113323643853605</v>
       </c>
       <c r="T40">
-        <v>1.029950734056311</v>
+        <v>1.044569295323167</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.686449273743573</v>
+        <v>3.591924933391174</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08638102275069906</v>
+        <v>0.08627607476208585</v>
       </c>
       <c r="C41">
-        <v>11894.23829682648</v>
+        <v>11755.98644177196</v>
       </c>
       <c r="D41">
-        <v>17038.91429682648</v>
+        <v>17075.44644177196</v>
       </c>
       <c r="E41">
-        <v>-627.3239999999987</v>
+        <v>-452.5399999999991</v>
       </c>
       <c r="F41">
-        <v>6816.576000000001</v>
+        <v>6991.360000000001</v>
       </c>
       <c r="G41">
         <v>1671.9</v>
@@ -4655,28 +4655,28 @@
         <v>1354</v>
       </c>
       <c r="M41">
-        <v>376.9566528000001</v>
+        <v>386.6222080000001</v>
       </c>
       <c r="N41">
-        <v>977.0433472</v>
+        <v>967.377792</v>
       </c>
       <c r="O41">
-        <v>195.40866944</v>
+        <v>193.4755584</v>
       </c>
       <c r="P41">
-        <v>781.6346777599999</v>
+        <v>773.9022336</v>
       </c>
       <c r="Q41">
-        <v>1028.73467776</v>
+        <v>1021.0022336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.113323643853605</v>
+        <v>0.1143001246034764</v>
       </c>
       <c r="T41">
-        <v>1.044569295323167</v>
+        <v>1.059675141965585</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.591924933391174</v>
+        <v>3.502126810056394</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08627607476208585</v>
+        <v>0.08617112677347262</v>
       </c>
       <c r="C42">
-        <v>11755.98644177196</v>
+        <v>11617.89157620308</v>
       </c>
       <c r="D42">
-        <v>17075.44644177196</v>
+        <v>17112.13557620308</v>
       </c>
       <c r="E42">
-        <v>-452.5399999999991</v>
+        <v>-277.7559999999985</v>
       </c>
       <c r="F42">
-        <v>6991.360000000001</v>
+        <v>7166.144000000001</v>
       </c>
       <c r="G42">
         <v>1671.9</v>
@@ -4737,28 +4737,28 @@
         <v>1354</v>
       </c>
       <c r="M42">
-        <v>386.6222080000001</v>
+        <v>396.2877632000001</v>
       </c>
       <c r="N42">
-        <v>967.377792</v>
+        <v>957.7122367999999</v>
       </c>
       <c r="O42">
-        <v>193.4755584</v>
+        <v>191.54244736</v>
       </c>
       <c r="P42">
-        <v>773.9022336</v>
+        <v>766.1697894399999</v>
       </c>
       <c r="Q42">
-        <v>1021.0022336</v>
+        <v>1013.26978944</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1143001246034764</v>
+        <v>0.1153097063957163</v>
       </c>
       <c r="T42">
-        <v>1.059675141965585</v>
+        <v>1.07529305120605</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.502126810056394</v>
+        <v>3.416709082981848</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08617112677347262</v>
+        <v>0.08606617878485939</v>
       </c>
       <c r="C43">
-        <v>11617.89157620308</v>
+        <v>11479.95471424456</v>
       </c>
       <c r="D43">
-        <v>17112.13557620308</v>
+        <v>17148.98271424456</v>
       </c>
       <c r="E43">
-        <v>-277.7559999999985</v>
+        <v>-102.9719999999979</v>
       </c>
       <c r="F43">
-        <v>7166.144000000001</v>
+        <v>7340.928000000002</v>
       </c>
       <c r="G43">
         <v>1671.9</v>
@@ -4819,28 +4819,28 @@
         <v>1354</v>
       </c>
       <c r="M43">
-        <v>396.2877632000001</v>
+        <v>405.9533184000001</v>
       </c>
       <c r="N43">
-        <v>957.7122367999999</v>
+        <v>948.0466815999998</v>
       </c>
       <c r="O43">
-        <v>191.54244736</v>
+        <v>189.60933632</v>
       </c>
       <c r="P43">
-        <v>766.1697894399999</v>
+        <v>758.4373452799998</v>
       </c>
       <c r="Q43">
-        <v>1013.26978944</v>
+        <v>1005.53734528</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1153097063957163</v>
+        <v>0.1163541013532058</v>
       </c>
       <c r="T43">
-        <v>1.07529305120605</v>
+        <v>1.091449509041015</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.416709082981848</v>
+        <v>3.335358866720375</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08606617878485939</v>
+        <v>0.08596123079624618</v>
       </c>
       <c r="C44">
-        <v>11479.95471424457</v>
+        <v>11342.17687877474</v>
       </c>
       <c r="D44">
-        <v>17148.98271424456</v>
+        <v>17185.98887877474</v>
       </c>
       <c r="E44">
-        <v>-102.9719999999988</v>
+        <v>71.81200000000081</v>
       </c>
       <c r="F44">
-        <v>7340.928000000001</v>
+        <v>7515.712</v>
       </c>
       <c r="G44">
         <v>1671.9</v>
@@ -4901,28 +4901,28 @@
         <v>1354</v>
       </c>
       <c r="M44">
-        <v>405.9533184000001</v>
+        <v>415.6188736</v>
       </c>
       <c r="N44">
-        <v>948.0466815999999</v>
+        <v>938.3811264</v>
       </c>
       <c r="O44">
-        <v>189.60933632</v>
+        <v>187.67622528</v>
       </c>
       <c r="P44">
-        <v>758.4373452799999</v>
+        <v>750.7049011199999</v>
       </c>
       <c r="Q44">
-        <v>1005.53734528</v>
+        <v>997.8049011199998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1163541013532058</v>
+        <v>0.1174351417478003</v>
       </c>
       <c r="T44">
-        <v>1.091449509041014</v>
+        <v>1.108172860133346</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.335358866720376</v>
+        <v>3.257792381447809</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08596123079624618</v>
+        <v>0.08585628280763292</v>
       </c>
       <c r="C45">
-        <v>11342.17687877474</v>
+        <v>11204.5591015202</v>
       </c>
       <c r="D45">
-        <v>17185.98887877474</v>
+        <v>17223.1551015202</v>
       </c>
       <c r="E45">
-        <v>71.81200000000081</v>
+        <v>246.5960000000014</v>
       </c>
       <c r="F45">
-        <v>7515.712</v>
+        <v>7690.496000000001</v>
       </c>
       <c r="G45">
         <v>1671.9</v>
@@ -4983,28 +4983,28 @@
         <v>1354</v>
       </c>
       <c r="M45">
-        <v>415.6188736</v>
+        <v>425.2844288000001</v>
       </c>
       <c r="N45">
-        <v>938.3811264</v>
+        <v>928.7155711999999</v>
       </c>
       <c r="O45">
-        <v>187.67622528</v>
+        <v>185.74311424</v>
       </c>
       <c r="P45">
-        <v>750.7049011199999</v>
+        <v>742.9724569599999</v>
       </c>
       <c r="Q45">
-        <v>997.8049011199998</v>
+        <v>990.0724569599998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1174351417478003</v>
+        <v>0.1185547907279159</v>
       </c>
       <c r="T45">
-        <v>1.108172860133346</v>
+        <v>1.125493473764689</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.257792381447809</v>
+        <v>3.183751645505813</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08585628280763292</v>
+        <v>0.0857513348190197</v>
       </c>
       <c r="C46">
-        <v>11204.5591015202</v>
+        <v>11067.10242315167</v>
       </c>
       <c r="D46">
-        <v>17223.1551015202</v>
+        <v>17260.48242315166</v>
       </c>
       <c r="E46">
-        <v>246.5960000000014</v>
+        <v>421.380000000001</v>
       </c>
       <c r="F46">
-        <v>7690.496000000001</v>
+        <v>7865.280000000001</v>
       </c>
       <c r="G46">
         <v>1671.9</v>
@@ -5065,28 +5065,28 @@
         <v>1354</v>
       </c>
       <c r="M46">
-        <v>425.2844288000001</v>
+        <v>434.949984</v>
       </c>
       <c r="N46">
-        <v>928.7155711999999</v>
+        <v>919.0500159999999</v>
       </c>
       <c r="O46">
-        <v>185.74311424</v>
+        <v>183.8100032</v>
       </c>
       <c r="P46">
-        <v>742.9724569599999</v>
+        <v>735.2400127999999</v>
       </c>
       <c r="Q46">
-        <v>990.0724569599998</v>
+        <v>982.3400127999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1185547907279159</v>
+        <v>0.1197151542163994</v>
       </c>
       <c r="T46">
-        <v>1.125493473764689</v>
+        <v>1.143443927891718</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.183751645505813</v>
+        <v>3.113001608939018</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0857513348190197</v>
+        <v>0.08564638683040647</v>
       </c>
       <c r="C47">
-        <v>11067.10242315167</v>
+        <v>10929.80789338116</v>
       </c>
       <c r="D47">
-        <v>17260.48242315166</v>
+        <v>17297.97189338116</v>
       </c>
       <c r="E47">
-        <v>421.380000000001</v>
+        <v>596.1640000000016</v>
       </c>
       <c r="F47">
-        <v>7865.280000000001</v>
+        <v>8040.064000000001</v>
       </c>
       <c r="G47">
         <v>1671.9</v>
@@ -5147,28 +5147,28 @@
         <v>1354</v>
       </c>
       <c r="M47">
-        <v>434.949984</v>
+        <v>444.6155392000001</v>
       </c>
       <c r="N47">
-        <v>919.0500159999999</v>
+        <v>909.3844607999999</v>
       </c>
       <c r="O47">
-        <v>183.8100032</v>
+        <v>181.87689216</v>
       </c>
       <c r="P47">
-        <v>735.2400127999999</v>
+        <v>727.5075686399999</v>
       </c>
       <c r="Q47">
-        <v>982.3400127999998</v>
+        <v>974.6075686399998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1197151542163994</v>
+        <v>0.1209184941303823</v>
       </c>
       <c r="T47">
-        <v>1.143443927891718</v>
+        <v>1.162059213653081</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.113001608939018</v>
+        <v>3.045327660918604</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08564638683040647</v>
+        <v>0.08648143884179324</v>
       </c>
       <c r="C48">
-        <v>10929.80789338116</v>
+        <v>10461.15773390593</v>
       </c>
       <c r="D48">
-        <v>17297.97189338116</v>
+        <v>17004.10573390593</v>
       </c>
       <c r="E48">
-        <v>596.1640000000016</v>
+        <v>770.9480000000021</v>
       </c>
       <c r="F48">
-        <v>8040.064000000001</v>
+        <v>8214.848000000002</v>
       </c>
       <c r="G48">
         <v>1671.9</v>
@@ -5229,45 +5229,45 @@
         <v>1354</v>
       </c>
       <c r="M48">
-        <v>444.6155392000001</v>
+        <v>474.8182144000002</v>
       </c>
       <c r="N48">
-        <v>909.3844607999999</v>
+        <v>879.1817855999998</v>
       </c>
       <c r="O48">
-        <v>181.87689216</v>
+        <v>175.83635712</v>
       </c>
       <c r="P48">
-        <v>727.5075686399999</v>
+        <v>703.3454284799998</v>
       </c>
       <c r="Q48">
-        <v>974.6075686399998</v>
+        <v>950.4454284799997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1209184941303823</v>
+        <v>0.1221672430977231</v>
       </c>
       <c r="T48">
-        <v>1.162059213653081</v>
+        <v>1.18137696302808</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.045327660918604</v>
+        <v>2.851617648474101</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08648143884179324</v>
+        <v>0.08639649085317999</v>
       </c>
       <c r="C49">
-        <v>10461.15773390593</v>
+        <v>10315.81110058678</v>
       </c>
       <c r="D49">
-        <v>17004.10573390593</v>
+        <v>17033.54310058678</v>
       </c>
       <c r="E49">
-        <v>770.9480000000021</v>
+        <v>945.7320000000018</v>
       </c>
       <c r="F49">
-        <v>8214.848000000002</v>
+        <v>8389.632000000001</v>
       </c>
       <c r="G49">
         <v>1671.9</v>
@@ -5311,28 +5311,28 @@
         <v>1354</v>
       </c>
       <c r="M49">
-        <v>474.8182144000002</v>
+        <v>484.9207296000001</v>
       </c>
       <c r="N49">
-        <v>879.1817855999998</v>
+        <v>869.0792703999998</v>
       </c>
       <c r="O49">
-        <v>175.83635712</v>
+        <v>173.81585408</v>
       </c>
       <c r="P49">
-        <v>703.3454284799998</v>
+        <v>695.2634163199998</v>
       </c>
       <c r="Q49">
-        <v>950.4454284799997</v>
+        <v>942.3634163199997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1221672430977231</v>
+        <v>0.1234640208715</v>
       </c>
       <c r="T49">
-        <v>1.18137696302808</v>
+        <v>1.201437702763656</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.851617648474101</v>
+        <v>2.792208947464224</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08639649085317999</v>
+        <v>0.08631154286456677</v>
       </c>
       <c r="C50">
-        <v>10315.81110058678</v>
+        <v>10170.56656747228</v>
       </c>
       <c r="D50">
-        <v>17033.54310058678</v>
+        <v>17063.08256747228</v>
       </c>
       <c r="E50">
-        <v>945.732</v>
+        <v>1120.516000000001</v>
       </c>
       <c r="F50">
-        <v>8389.632</v>
+        <v>8564.416000000001</v>
       </c>
       <c r="G50">
         <v>1671.9</v>
@@ -5393,28 +5393,28 @@
         <v>1354</v>
       </c>
       <c r="M50">
-        <v>484.9207296</v>
+        <v>495.0232448000001</v>
       </c>
       <c r="N50">
-        <v>869.0792704</v>
+        <v>858.9767551999998</v>
       </c>
       <c r="O50">
-        <v>173.81585408</v>
+        <v>171.79535104</v>
       </c>
       <c r="P50">
-        <v>695.26341632</v>
+        <v>687.1814041599998</v>
       </c>
       <c r="Q50">
-        <v>942.3634163199999</v>
+        <v>934.2814041599997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1234640208715</v>
+        <v>0.1248116526756211</v>
       </c>
       <c r="T50">
-        <v>1.201437702763656</v>
+        <v>1.222285138175137</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.792208947464225</v>
+        <v>2.735225091393525</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08631154286456677</v>
+        <v>0.08622659487595355</v>
       </c>
       <c r="C51">
-        <v>10170.56656747228</v>
+        <v>10025.42466666987</v>
       </c>
       <c r="D51">
-        <v>17063.08256747228</v>
+        <v>17092.72466666987</v>
       </c>
       <c r="E51">
-        <v>1120.516000000001</v>
+        <v>1295.300000000001</v>
       </c>
       <c r="F51">
-        <v>8564.416000000001</v>
+        <v>8739.200000000001</v>
       </c>
       <c r="G51">
         <v>1671.9</v>
@@ -5475,28 +5475,28 @@
         <v>1354</v>
       </c>
       <c r="M51">
-        <v>495.0232448000001</v>
+        <v>505.1257600000001</v>
       </c>
       <c r="N51">
-        <v>858.9767551999998</v>
+        <v>848.8742399999999</v>
       </c>
       <c r="O51">
-        <v>171.79535104</v>
+        <v>169.774848</v>
       </c>
       <c r="P51">
-        <v>687.1814041599998</v>
+        <v>679.0993919999999</v>
       </c>
       <c r="Q51">
-        <v>934.2814041599997</v>
+        <v>926.1993919999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1248116526756211</v>
+        <v>0.1262131897519071</v>
       </c>
       <c r="T51">
-        <v>1.222285138175137</v>
+        <v>1.243966471003078</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.735225091393525</v>
+        <v>2.680520589565655</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08622659487595355</v>
+        <v>0.08614164688734031</v>
       </c>
       <c r="C52">
-        <v>10025.42466666987</v>
+        <v>9880.385933990961</v>
       </c>
       <c r="D52">
-        <v>17092.72466666987</v>
+        <v>17122.46993399096</v>
       </c>
       <c r="E52">
-        <v>1295.300000000001</v>
+        <v>1470.084000000001</v>
       </c>
       <c r="F52">
-        <v>8739.200000000001</v>
+        <v>8913.984</v>
       </c>
       <c r="G52">
         <v>1671.9</v>
@@ -5557,28 +5557,28 @@
         <v>1354</v>
       </c>
       <c r="M52">
-        <v>505.1257600000001</v>
+        <v>515.2282752000001</v>
       </c>
       <c r="N52">
-        <v>848.8742399999999</v>
+        <v>838.7717247999999</v>
       </c>
       <c r="O52">
-        <v>169.774848</v>
+        <v>167.75434496</v>
       </c>
       <c r="P52">
-        <v>679.0993919999999</v>
+        <v>671.0173798399999</v>
       </c>
       <c r="Q52">
-        <v>926.1993919999998</v>
+        <v>918.1173798399998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1262131897519071</v>
+        <v>0.1276719324231435</v>
       </c>
       <c r="T52">
-        <v>1.243966471003078</v>
+        <v>1.266532756191342</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.680520589565655</v>
+        <v>2.62796136231927</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08614164688734031</v>
+        <v>0.08605669889872708</v>
       </c>
       <c r="C53">
-        <v>9880.385933990961</v>
+        <v>9735.450908983172</v>
       </c>
       <c r="D53">
-        <v>17122.46993399096</v>
+        <v>17152.31890898317</v>
       </c>
       <c r="E53">
-        <v>1470.084000000001</v>
+        <v>1644.868000000002</v>
       </c>
       <c r="F53">
-        <v>8913.984</v>
+        <v>9088.768000000002</v>
       </c>
       <c r="G53">
         <v>1671.9</v>
@@ -5639,28 +5639,28 @@
         <v>1354</v>
       </c>
       <c r="M53">
-        <v>515.2282752000001</v>
+        <v>525.3307904000002</v>
       </c>
       <c r="N53">
-        <v>838.7717247999999</v>
+        <v>828.6692095999998</v>
       </c>
       <c r="O53">
-        <v>167.75434496</v>
+        <v>165.73384192</v>
       </c>
       <c r="P53">
-        <v>671.0173798399999</v>
+        <v>662.9353676799999</v>
       </c>
       <c r="Q53">
-        <v>918.1173798399998</v>
+        <v>910.0353676799998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1276719324231435</v>
+        <v>0.1291914560390147</v>
       </c>
       <c r="T53">
-        <v>1.266532756191342</v>
+        <v>1.290039303262451</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.62796136231927</v>
+        <v>2.577423643813129</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08605669889872708</v>
+        <v>0.08597175091011386</v>
       </c>
       <c r="C54">
-        <v>9735.450908983172</v>
+        <v>9590.620134963016</v>
       </c>
       <c r="D54">
-        <v>17152.31890898317</v>
+        <v>17182.27213496302</v>
       </c>
       <c r="E54">
-        <v>1644.868000000002</v>
+        <v>1819.652000000002</v>
       </c>
       <c r="F54">
-        <v>9088.768000000002</v>
+        <v>9263.552000000001</v>
       </c>
       <c r="G54">
         <v>1671.9</v>
@@ -5721,28 +5721,28 @@
         <v>1354</v>
       </c>
       <c r="M54">
-        <v>525.3307904000002</v>
+        <v>535.4333056000002</v>
       </c>
       <c r="N54">
-        <v>828.6692095999998</v>
+        <v>818.5666943999998</v>
       </c>
       <c r="O54">
-        <v>165.73384192</v>
+        <v>163.71333888</v>
       </c>
       <c r="P54">
-        <v>662.9353676799999</v>
+        <v>654.8533555199999</v>
       </c>
       <c r="Q54">
-        <v>910.0353676799998</v>
+        <v>901.9533555199998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1291914560390147</v>
+        <v>0.1307756402342848</v>
       </c>
       <c r="T54">
-        <v>1.290039303262451</v>
+        <v>1.31454612893233</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.577423643813129</v>
+        <v>2.528793009024203</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08597175091011386</v>
+        <v>0.08739880292150061</v>
       </c>
       <c r="C55">
-        <v>9590.620134963016</v>
+        <v>8926.13545612835</v>
       </c>
       <c r="D55">
-        <v>17182.27213496302</v>
+        <v>16692.57145612835</v>
       </c>
       <c r="E55">
-        <v>1819.652000000002</v>
+        <v>1994.436000000002</v>
       </c>
       <c r="F55">
-        <v>9263.552000000001</v>
+        <v>9438.336000000001</v>
       </c>
       <c r="G55">
         <v>1671.9</v>
@@ -5803,45 +5803,45 @@
         <v>1354</v>
       </c>
       <c r="M55">
-        <v>535.4333056000002</v>
+        <v>578.5699968000001</v>
       </c>
       <c r="N55">
-        <v>818.5666943999998</v>
+        <v>775.4300031999999</v>
       </c>
       <c r="O55">
-        <v>163.71333888</v>
+        <v>155.08600064</v>
       </c>
       <c r="P55">
-        <v>654.8533555199999</v>
+        <v>620.3440025599999</v>
       </c>
       <c r="Q55">
-        <v>901.9533555199998</v>
+        <v>867.4440025599998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1307756402342848</v>
+        <v>0.1324287020032622</v>
       </c>
       <c r="T55">
-        <v>1.31454612893233</v>
+        <v>1.34011846876177</v>
       </c>
       <c r="U55">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.528793009024203</v>
+        <v>2.340252704925607</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08739880292150061</v>
+        <v>0.0873418549328874</v>
       </c>
       <c r="C56">
-        <v>8926.13545612835</v>
+        <v>8770.358131805731</v>
       </c>
       <c r="D56">
-        <v>16692.57145612835</v>
+        <v>16711.57813180573</v>
       </c>
       <c r="E56">
-        <v>1994.436000000002</v>
+        <v>2169.220000000001</v>
       </c>
       <c r="F56">
-        <v>9438.336000000001</v>
+        <v>9613.120000000001</v>
       </c>
       <c r="G56">
         <v>1671.9</v>
@@ -5885,28 +5885,28 @@
         <v>1354</v>
       </c>
       <c r="M56">
-        <v>578.5699968000001</v>
+        <v>589.284256</v>
       </c>
       <c r="N56">
-        <v>775.4300031999999</v>
+        <v>764.715744</v>
       </c>
       <c r="O56">
-        <v>155.08600064</v>
+        <v>152.9431488</v>
       </c>
       <c r="P56">
-        <v>620.3440025599999</v>
+        <v>611.7725952</v>
       </c>
       <c r="Q56">
-        <v>867.4440025599998</v>
+        <v>858.8725951999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1324287020032622</v>
+        <v>0.1341552331841942</v>
       </c>
       <c r="T56">
-        <v>1.34011846876177</v>
+        <v>1.366827357028073</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.340252704925607</v>
+        <v>2.297702655745142</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0873418549328874</v>
+        <v>0.08728490694427417</v>
       </c>
       <c r="C57">
-        <v>8770.358131805731</v>
+        <v>8614.624139994794</v>
       </c>
       <c r="D57">
-        <v>16711.57813180573</v>
+        <v>16730.62813999479</v>
       </c>
       <c r="E57">
-        <v>2169.220000000001</v>
+        <v>2344.004000000003</v>
       </c>
       <c r="F57">
-        <v>9613.120000000001</v>
+        <v>9787.904000000002</v>
       </c>
       <c r="G57">
         <v>1671.9</v>
@@ -5967,28 +5967,28 @@
         <v>1354</v>
       </c>
       <c r="M57">
-        <v>589.284256</v>
+        <v>599.9985152000002</v>
       </c>
       <c r="N57">
-        <v>764.715744</v>
+        <v>754.0014847999998</v>
       </c>
       <c r="O57">
-        <v>152.9431488</v>
+        <v>150.80029696</v>
       </c>
       <c r="P57">
-        <v>611.7725952</v>
+        <v>603.2011878399999</v>
       </c>
       <c r="Q57">
-        <v>858.8725951999999</v>
+        <v>850.3011878399998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1341552331841942</v>
+        <v>0.1359602430551686</v>
       </c>
       <c r="T57">
-        <v>1.366827357028073</v>
+        <v>1.394750285670117</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.297702655745142</v>
+        <v>2.256672251178264</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08728490694427417</v>
+        <v>0.08850475895566093</v>
       </c>
       <c r="C58">
-        <v>8614.624139994794</v>
+        <v>8041.052589123803</v>
       </c>
       <c r="D58">
-        <v>16730.62813999479</v>
+        <v>16331.84058912381</v>
       </c>
       <c r="E58">
-        <v>2344.004000000003</v>
+        <v>2518.788000000002</v>
       </c>
       <c r="F58">
-        <v>9787.904000000002</v>
+        <v>9962.688000000002</v>
       </c>
       <c r="G58">
         <v>1671.9</v>
@@ -6049,45 +6049,45 @@
         <v>1354</v>
       </c>
       <c r="M58">
-        <v>599.9985152000002</v>
+        <v>638.6083008000002</v>
       </c>
       <c r="N58">
-        <v>754.0014847999998</v>
+        <v>715.3916991999998</v>
       </c>
       <c r="O58">
-        <v>150.80029696</v>
+        <v>143.07833984</v>
       </c>
       <c r="P58">
-        <v>603.2011878399999</v>
+        <v>572.3133593599998</v>
       </c>
       <c r="Q58">
-        <v>850.3011878399998</v>
+        <v>819.4133593599997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1359602430551686</v>
+        <v>0.1378492068736301</v>
       </c>
       <c r="T58">
-        <v>1.394750285670117</v>
+        <v>1.423971955179234</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.256672251178264</v>
+        <v>2.120235515736033</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08850475895566093</v>
+        <v>0.0884702109670477</v>
       </c>
       <c r="C59">
-        <v>8041.052589123803</v>
+        <v>7877.301074862047</v>
       </c>
       <c r="D59">
-        <v>16331.84058912381</v>
+        <v>16342.87307486205</v>
       </c>
       <c r="E59">
-        <v>2518.788000000002</v>
+        <v>2693.572000000002</v>
       </c>
       <c r="F59">
-        <v>9962.688000000002</v>
+        <v>10137.472</v>
       </c>
       <c r="G59">
         <v>1671.9</v>
@@ -6131,28 +6131,28 @@
         <v>1354</v>
       </c>
       <c r="M59">
-        <v>638.6083008000002</v>
+        <v>649.8119552000002</v>
       </c>
       <c r="N59">
-        <v>715.3916991999998</v>
+        <v>704.1880447999998</v>
       </c>
       <c r="O59">
-        <v>143.07833984</v>
+        <v>140.83760896</v>
       </c>
       <c r="P59">
-        <v>572.3133593599998</v>
+        <v>563.3504358399998</v>
       </c>
       <c r="Q59">
-        <v>819.4133593599997</v>
+        <v>810.4504358399997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1378492068736301</v>
+        <v>0.1398281213501136</v>
       </c>
       <c r="T59">
-        <v>1.423971955179234</v>
+        <v>1.454585132760213</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.120235515736033</v>
+        <v>2.083679730981963</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0884702109670477</v>
+        <v>0.08843566297843447</v>
       </c>
       <c r="C60">
-        <v>7877.301074862049</v>
+        <v>7713.564476006533</v>
       </c>
       <c r="D60">
-        <v>16342.87307486205</v>
+        <v>16353.92047600653</v>
       </c>
       <c r="E60">
-        <v>2693.572</v>
+        <v>2868.356000000002</v>
       </c>
       <c r="F60">
-        <v>10137.472</v>
+        <v>10312.256</v>
       </c>
       <c r="G60">
         <v>1671.9</v>
@@ -6213,28 +6213,28 @@
         <v>1354</v>
       </c>
       <c r="M60">
-        <v>649.8119552000001</v>
+        <v>661.0156096000002</v>
       </c>
       <c r="N60">
-        <v>704.1880447999999</v>
+        <v>692.9843903999998</v>
       </c>
       <c r="O60">
-        <v>140.83760896</v>
+        <v>138.59687808</v>
       </c>
       <c r="P60">
-        <v>563.3504358399999</v>
+        <v>554.3875123199998</v>
       </c>
       <c r="Q60">
-        <v>810.4504358399998</v>
+        <v>801.4875123199997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1398281213501135</v>
+        <v>0.1419035682400841</v>
       </c>
       <c r="T60">
-        <v>1.454585132760212</v>
+        <v>1.486691636076849</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.083679730981964</v>
+        <v>2.0483631253721</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08843566297843447</v>
+        <v>0.08840111498982126</v>
       </c>
       <c r="C61">
-        <v>7713.564476006533</v>
+        <v>7549.842822825125</v>
       </c>
       <c r="D61">
-        <v>16353.92047600653</v>
+        <v>16364.98282282513</v>
       </c>
       <c r="E61">
-        <v>2868.356000000002</v>
+        <v>3043.140000000001</v>
       </c>
       <c r="F61">
-        <v>10312.256</v>
+        <v>10487.04</v>
       </c>
       <c r="G61">
         <v>1671.9</v>
@@ -6295,28 +6295,28 @@
         <v>1354</v>
       </c>
       <c r="M61">
-        <v>661.0156096000002</v>
+        <v>672.2192640000001</v>
       </c>
       <c r="N61">
-        <v>692.9843903999998</v>
+        <v>681.7807359999999</v>
       </c>
       <c r="O61">
-        <v>138.59687808</v>
+        <v>136.3561472</v>
       </c>
       <c r="P61">
-        <v>554.3875123199998</v>
+        <v>545.4245887999999</v>
       </c>
       <c r="Q61">
-        <v>801.4875123199997</v>
+        <v>792.5245887999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1419035682400841</v>
+        <v>0.1440827874745531</v>
       </c>
       <c r="T61">
-        <v>1.486691636076849</v>
+        <v>1.520403464559317</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.0483631253721</v>
+        <v>2.014223739949232</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08840111498982126</v>
+        <v>0.09217296700120803</v>
       </c>
       <c r="C62">
-        <v>7549.842822825125</v>
+        <v>6249.602274142984</v>
       </c>
       <c r="D62">
-        <v>16364.98282282513</v>
+        <v>15239.52627414298</v>
       </c>
       <c r="E62">
-        <v>3043.140000000001</v>
+        <v>3217.924000000001</v>
       </c>
       <c r="F62">
-        <v>10487.04</v>
+        <v>10661.824</v>
       </c>
       <c r="G62">
         <v>1671.9</v>
@@ -6377,45 +6377,45 @@
         <v>1354</v>
       </c>
       <c r="M62">
-        <v>672.2192640000001</v>
+        <v>766.5851456000001</v>
       </c>
       <c r="N62">
-        <v>681.7807359999999</v>
+        <v>587.4148543999999</v>
       </c>
       <c r="O62">
-        <v>136.3561472</v>
+        <v>117.48297088</v>
       </c>
       <c r="P62">
-        <v>545.4245887999999</v>
+        <v>469.9318835199999</v>
       </c>
       <c r="Q62">
-        <v>792.5245887999998</v>
+        <v>717.0318835199998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1440827874745531</v>
+        <v>0.146373761541559</v>
       </c>
       <c r="T62">
-        <v>1.520403464559317</v>
+        <v>1.555844104758835</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.014223739949232</v>
+        <v>1.766274767743164</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09217296700120803</v>
+        <v>0.09413521901259478</v>
       </c>
       <c r="C63">
-        <v>6249.602274142984</v>
+        <v>5548.415467393163</v>
       </c>
       <c r="D63">
-        <v>15239.52627414298</v>
+        <v>14713.12346739316</v>
       </c>
       <c r="E63">
-        <v>3217.924000000001</v>
+        <v>3392.708000000001</v>
       </c>
       <c r="F63">
-        <v>10661.824</v>
+        <v>10836.608</v>
       </c>
       <c r="G63">
         <v>1671.9</v>
@@ -6459,45 +6459,45 @@
         <v>1354</v>
       </c>
       <c r="M63">
-        <v>766.5851456000001</v>
+        <v>821.4148864000001</v>
       </c>
       <c r="N63">
-        <v>587.4148543999999</v>
+        <v>532.5851135999999</v>
       </c>
       <c r="O63">
-        <v>117.48297088</v>
+        <v>106.51702272</v>
       </c>
       <c r="P63">
-        <v>469.9318835199999</v>
+        <v>426.0680908799999</v>
       </c>
       <c r="Q63">
-        <v>717.0318835199998</v>
+        <v>673.1680908799998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.146373761541559</v>
+        <v>0.1487853131910389</v>
       </c>
       <c r="T63">
-        <v>1.555844104758835</v>
+        <v>1.593150041810959</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.766274767743164</v>
+        <v>1.64837528807659</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09413521901259478</v>
+        <v>0.09419427102398156</v>
       </c>
       <c r="C64">
-        <v>5548.415467393163</v>
+        <v>5358.35298198702</v>
       </c>
       <c r="D64">
-        <v>14713.12346739316</v>
+        <v>14697.84498198702</v>
       </c>
       <c r="E64">
-        <v>3392.708000000001</v>
+        <v>3567.492000000002</v>
       </c>
       <c r="F64">
-        <v>10836.608</v>
+        <v>11011.392</v>
       </c>
       <c r="G64">
         <v>1671.9</v>
@@ -6541,28 +6541,28 @@
         <v>1354</v>
       </c>
       <c r="M64">
-        <v>821.4148864000001</v>
+        <v>834.6635136000002</v>
       </c>
       <c r="N64">
-        <v>532.5851135999999</v>
+        <v>519.3364863999998</v>
       </c>
       <c r="O64">
-        <v>106.51702272</v>
+        <v>103.86729728</v>
       </c>
       <c r="P64">
-        <v>426.0680908799999</v>
+        <v>415.4691891199998</v>
       </c>
       <c r="Q64">
-        <v>673.1680908799998</v>
+        <v>662.5691891199997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1487853131910389</v>
+        <v>0.1513272189837339</v>
       </c>
       <c r="T64">
-        <v>1.593150041810959</v>
+        <v>1.632472516001036</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.64837528807659</v>
+        <v>1.622210600964263</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09419427102398156</v>
+        <v>0.09425332303536833</v>
       </c>
       <c r="C65">
-        <v>5358.35298198702</v>
+        <v>5168.322194808165</v>
       </c>
       <c r="D65">
-        <v>14697.84498198702</v>
+        <v>14682.59819480817</v>
       </c>
       <c r="E65">
-        <v>3567.492000000002</v>
+        <v>3742.276000000002</v>
       </c>
       <c r="F65">
-        <v>11011.392</v>
+        <v>11186.176</v>
       </c>
       <c r="G65">
         <v>1671.9</v>
@@ -6623,28 +6623,28 @@
         <v>1354</v>
       </c>
       <c r="M65">
-        <v>834.6635136000002</v>
+        <v>847.9121408000002</v>
       </c>
       <c r="N65">
-        <v>519.3364863999998</v>
+        <v>506.0878591999998</v>
       </c>
       <c r="O65">
-        <v>103.86729728</v>
+        <v>101.21757184</v>
       </c>
       <c r="P65">
-        <v>415.4691891199998</v>
+        <v>404.8702873599998</v>
       </c>
       <c r="Q65">
-        <v>662.5691891199997</v>
+        <v>651.9702873599997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1513272189837339</v>
+        <v>0.154010341764912</v>
       </c>
       <c r="T65">
-        <v>1.632472516001036</v>
+        <v>1.673979572090561</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.622210600964263</v>
+        <v>1.596863560324197</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09425332303536833</v>
+        <v>0.09431237504675509</v>
       </c>
       <c r="C66">
-        <v>5168.322194808165</v>
+        <v>4978.323007312496</v>
       </c>
       <c r="D66">
-        <v>14682.59819480817</v>
+        <v>14667.3830073125</v>
       </c>
       <c r="E66">
-        <v>3742.276000000002</v>
+        <v>3917.060000000001</v>
       </c>
       <c r="F66">
-        <v>11186.176</v>
+        <v>11360.96</v>
       </c>
       <c r="G66">
         <v>1671.9</v>
@@ -6705,28 +6705,28 @@
         <v>1354</v>
       </c>
       <c r="M66">
-        <v>847.9121408000002</v>
+        <v>861.1607680000002</v>
       </c>
       <c r="N66">
-        <v>506.0878591999998</v>
+        <v>492.8392319999998</v>
       </c>
       <c r="O66">
-        <v>101.21757184</v>
+        <v>98.56784639999997</v>
       </c>
       <c r="P66">
-        <v>404.8702873599998</v>
+        <v>394.2713855999999</v>
       </c>
       <c r="Q66">
-        <v>651.9702873599997</v>
+        <v>641.3713855999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.154010341764912</v>
+        <v>0.1568467858478717</v>
       </c>
       <c r="T66">
-        <v>1.673979572090561</v>
+        <v>1.717858459956631</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.596863560324197</v>
+        <v>1.572296428626902</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09431237504675509</v>
+        <v>0.09437142705814186</v>
       </c>
       <c r="C67">
-        <v>4978.323007312496</v>
+        <v>4788.355321363959</v>
       </c>
       <c r="D67">
-        <v>14667.3830073125</v>
+        <v>14652.19932136396</v>
       </c>
       <c r="E67">
-        <v>3917.060000000001</v>
+        <v>4091.844000000001</v>
       </c>
       <c r="F67">
-        <v>11360.96</v>
+        <v>11535.744</v>
       </c>
       <c r="G67">
         <v>1671.9</v>
@@ -6787,28 +6787,28 @@
         <v>1354</v>
       </c>
       <c r="M67">
-        <v>861.1607680000002</v>
+        <v>874.4093952000001</v>
       </c>
       <c r="N67">
-        <v>492.8392319999998</v>
+        <v>479.5906047999999</v>
       </c>
       <c r="O67">
-        <v>98.56784639999997</v>
+        <v>95.91812096</v>
       </c>
       <c r="P67">
-        <v>394.2713855999999</v>
+        <v>383.6724838399999</v>
       </c>
       <c r="Q67">
-        <v>641.3713855999997</v>
+        <v>630.7724838399998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1568467858478717</v>
+        <v>0.1598500795827702</v>
       </c>
       <c r="T67">
-        <v>1.717858459956631</v>
+        <v>1.764318458873646</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.572296428626902</v>
+        <v>1.548473755465888</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09437142705814186</v>
+        <v>0.09443047906952864</v>
       </c>
       <c r="C68">
-        <v>4788.355321363959</v>
+        <v>4598.419039232449</v>
       </c>
       <c r="D68">
-        <v>14652.19932136396</v>
+        <v>14637.04703923245</v>
       </c>
       <c r="E68">
-        <v>4091.844000000001</v>
+        <v>4266.628000000002</v>
       </c>
       <c r="F68">
-        <v>11535.744</v>
+        <v>11710.528</v>
       </c>
       <c r="G68">
         <v>1671.9</v>
@@ -6869,28 +6869,28 @@
         <v>1354</v>
       </c>
       <c r="M68">
-        <v>874.4093952000001</v>
+        <v>887.6580224000003</v>
       </c>
       <c r="N68">
-        <v>479.5906047999999</v>
+        <v>466.3419775999997</v>
       </c>
       <c r="O68">
-        <v>95.91812096</v>
+        <v>93.26839551999996</v>
       </c>
       <c r="P68">
-        <v>383.6724838399999</v>
+        <v>373.0735820799998</v>
       </c>
       <c r="Q68">
-        <v>630.7724838399998</v>
+        <v>620.1735820799997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1598500795827702</v>
+        <v>0.1630353911197838</v>
       </c>
       <c r="T68">
-        <v>1.764318458873646</v>
+        <v>1.813594215300784</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.548473755465888</v>
+        <v>1.525362206876845</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09443047906952864</v>
+        <v>0.0944895310809154</v>
       </c>
       <c r="C69">
-        <v>4598.419039232449</v>
+        <v>4408.514063591716</v>
       </c>
       <c r="D69">
-        <v>14637.04703923245</v>
+        <v>14621.92606359172</v>
       </c>
       <c r="E69">
-        <v>4266.628000000002</v>
+        <v>4441.412000000002</v>
       </c>
       <c r="F69">
-        <v>11710.528</v>
+        <v>11885.312</v>
       </c>
       <c r="G69">
         <v>1671.9</v>
@@ -6951,28 +6951,28 @@
         <v>1354</v>
       </c>
       <c r="M69">
-        <v>887.6580224000003</v>
+        <v>900.9066496000002</v>
       </c>
       <c r="N69">
-        <v>466.3419775999997</v>
+        <v>453.0933503999998</v>
       </c>
       <c r="O69">
-        <v>93.26839551999996</v>
+        <v>90.61867007999997</v>
       </c>
       <c r="P69">
-        <v>373.0735820799998</v>
+        <v>362.4746803199999</v>
       </c>
       <c r="Q69">
-        <v>620.1735820799997</v>
+        <v>609.5746803199997</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1630353911197838</v>
+        <v>0.1664197846278606</v>
       </c>
       <c r="T69">
-        <v>1.813594215300784</v>
+        <v>1.865949706504616</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.525362206876845</v>
+        <v>1.502930409716891</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0944895310809154</v>
+        <v>0.1193765611353541</v>
       </c>
       <c r="C70">
-        <v>4408.514063591716</v>
+        <v>-201.3713378570992</v>
       </c>
       <c r="D70">
-        <v>14621.92606359172</v>
+        <v>10186.8246621429</v>
       </c>
       <c r="E70">
-        <v>4441.412000000002</v>
+        <v>4616.196000000002</v>
       </c>
       <c r="F70">
-        <v>11885.312</v>
+        <v>12060.096</v>
       </c>
       <c r="G70">
         <v>1671.9</v>
@@ -7033,45 +7033,45 @@
         <v>1354</v>
       </c>
       <c r="M70">
-        <v>900.9066496000002</v>
+        <v>1430.3273856</v>
       </c>
       <c r="N70">
-        <v>453.0933503999998</v>
+        <v>-76.3273856000003</v>
       </c>
       <c r="O70">
-        <v>90.61867007999997</v>
+        <v>-15.26547712000006</v>
       </c>
       <c r="P70">
-        <v>362.4746803199999</v>
+        <v>-61.06190848000024</v>
       </c>
       <c r="Q70">
-        <v>609.5746803199997</v>
+        <v>186.0380915199997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1664197846278606</v>
+        <v>0.1710837746549792</v>
       </c>
       <c r="T70">
-        <v>1.865949706504616</v>
+        <v>1.938100148897566</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2</v>
+        <v>0.1893272845967384</v>
       </c>
       <c r="W70">
-        <v>0.06064000000000001</v>
+        <v>0.09614578404682683</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.502930409716891</v>
+        <v>0.9466364229836919</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1193765611353541</v>
+        <v>0.1201045611353541</v>
       </c>
       <c r="C71">
-        <v>-201.3713378570992</v>
+        <v>-465.7453767322477</v>
       </c>
       <c r="D71">
-        <v>10186.8246621429</v>
+        <v>10097.23462326776</v>
       </c>
       <c r="E71">
-        <v>4616.196000000002</v>
+        <v>4790.980000000003</v>
       </c>
       <c r="F71">
-        <v>12060.096</v>
+        <v>12234.88</v>
       </c>
       <c r="G71">
         <v>1671.9</v>
@@ -7115,37 +7115,37 @@
         <v>1354</v>
       </c>
       <c r="M71">
-        <v>1430.3273856</v>
+        <v>1451.056768</v>
       </c>
       <c r="N71">
-        <v>-76.3273856000003</v>
+        <v>-97.05676800000037</v>
       </c>
       <c r="O71">
-        <v>-15.26547712000006</v>
+        <v>-19.41135360000008</v>
       </c>
       <c r="P71">
-        <v>-61.06190848000024</v>
+        <v>-77.64541440000031</v>
       </c>
       <c r="Q71">
-        <v>186.0380915199997</v>
+        <v>169.4545855999996</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1710837746549792</v>
+        <v>0.1752599004768119</v>
       </c>
       <c r="T71">
-        <v>1.938100148897566</v>
+        <v>2.002703487194151</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.1893272845967384</v>
+        <v>0.1866226091024993</v>
       </c>
       <c r="W71">
-        <v>0.09614578404682683</v>
+        <v>0.09646655856044359</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9466364229836919</v>
+        <v>0.9331130455124962</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1201045611353541</v>
+        <v>0.1208325611353541</v>
       </c>
       <c r="C72">
-        <v>-465.7453767322477</v>
+        <v>-728.5573192344546</v>
       </c>
       <c r="D72">
-        <v>10097.23462326776</v>
+        <v>10009.20668076555</v>
       </c>
       <c r="E72">
-        <v>4790.980000000003</v>
+        <v>4965.764000000003</v>
       </c>
       <c r="F72">
-        <v>12234.88</v>
+        <v>12409.664</v>
       </c>
       <c r="G72">
         <v>1671.9</v>
@@ -7197,37 +7197,37 @@
         <v>1354</v>
       </c>
       <c r="M72">
-        <v>1451.056768</v>
+        <v>1471.7861504</v>
       </c>
       <c r="N72">
-        <v>-97.05676800000037</v>
+        <v>-117.7861504000005</v>
       </c>
       <c r="O72">
-        <v>-19.41135360000008</v>
+        <v>-23.55723008000009</v>
       </c>
       <c r="P72">
-        <v>-77.64541440000031</v>
+        <v>-94.22892032000036</v>
       </c>
       <c r="Q72">
-        <v>169.4545855999996</v>
+        <v>152.8710796799996</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1752599004768119</v>
+        <v>0.1797240349760123</v>
       </c>
       <c r="T72">
-        <v>2.002703487194151</v>
+        <v>2.071762228131881</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.1866226091024993</v>
+        <v>0.1839941216503514</v>
       </c>
       <c r="W72">
-        <v>0.09646655856044359</v>
+        <v>0.09677829717226834</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9331130455124962</v>
+        <v>0.9199706082517568</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1208325611353541</v>
+        <v>0.1215605611353541</v>
       </c>
       <c r="C73">
-        <v>-728.5573192344527</v>
+        <v>-989.8476674505728</v>
       </c>
       <c r="D73">
-        <v>10009.20668076555</v>
+        <v>9922.700332549428</v>
       </c>
       <c r="E73">
-        <v>4965.764000000001</v>
+        <v>5140.548000000001</v>
       </c>
       <c r="F73">
-        <v>12409.664</v>
+        <v>12584.448</v>
       </c>
       <c r="G73">
         <v>1671.9</v>
@@ -7279,37 +7279,37 @@
         <v>1354</v>
       </c>
       <c r="M73">
-        <v>1471.7861504</v>
+        <v>1492.5155328</v>
       </c>
       <c r="N73">
-        <v>-117.7861504000002</v>
+        <v>-138.5155328000001</v>
       </c>
       <c r="O73">
-        <v>-23.55723008000005</v>
+        <v>-27.70310656000002</v>
       </c>
       <c r="P73">
-        <v>-94.22892032000019</v>
+        <v>-110.8124262400001</v>
       </c>
       <c r="Q73">
-        <v>152.8710796799997</v>
+        <v>136.2875737599998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1797240349760123</v>
+        <v>0.1845070362251555</v>
       </c>
       <c r="T73">
-        <v>2.071762228131881</v>
+        <v>2.145753736279447</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.1839941216503514</v>
+        <v>0.181438647738541</v>
       </c>
       <c r="W73">
-        <v>0.09677829717226834</v>
+        <v>0.09708137637820904</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9199706082517569</v>
+        <v>0.9071932386927049</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1215605611353541</v>
+        <v>0.1222885611353541</v>
       </c>
       <c r="C74">
-        <v>-989.8476674505728</v>
+        <v>-1249.655535279186</v>
       </c>
       <c r="D74">
-        <v>9922.700332549428</v>
+        <v>9837.676464720815</v>
       </c>
       <c r="E74">
-        <v>5140.548000000001</v>
+        <v>5315.332</v>
       </c>
       <c r="F74">
-        <v>12584.448</v>
+        <v>12759.232</v>
       </c>
       <c r="G74">
         <v>1671.9</v>
@@ -7361,37 +7361,37 @@
         <v>1354</v>
       </c>
       <c r="M74">
-        <v>1492.5155328</v>
+        <v>1513.2449152</v>
       </c>
       <c r="N74">
-        <v>-138.5155328000001</v>
+        <v>-159.2449152000002</v>
       </c>
       <c r="O74">
-        <v>-27.70310656000002</v>
+        <v>-31.84898304000003</v>
       </c>
       <c r="P74">
-        <v>-110.8124262400001</v>
+        <v>-127.3959321600001</v>
       </c>
       <c r="Q74">
-        <v>136.2875737599998</v>
+        <v>119.7040678399998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1845070362251555</v>
+        <v>0.1896443338631243</v>
       </c>
       <c r="T74">
-        <v>2.145753736279447</v>
+        <v>2.22522609688239</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.181438647738541</v>
+        <v>0.1789531868106158</v>
       </c>
       <c r="W74">
-        <v>0.09708137637820904</v>
+        <v>0.09737615204426098</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9071932386927049</v>
+        <v>0.8947659340530787</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1222885611353541</v>
+        <v>0.1230165611353541</v>
       </c>
       <c r="C75">
-        <v>-1249.655535279186</v>
+        <v>-1508.018707399604</v>
       </c>
       <c r="D75">
-        <v>9837.676464720815</v>
+        <v>9754.097292600398</v>
       </c>
       <c r="E75">
-        <v>5315.332</v>
+        <v>5490.116000000002</v>
       </c>
       <c r="F75">
-        <v>12759.232</v>
+        <v>12934.016</v>
       </c>
       <c r="G75">
         <v>1671.9</v>
@@ -7443,37 +7443,37 @@
         <v>1354</v>
       </c>
       <c r="M75">
-        <v>1513.2449152</v>
+        <v>1533.9742976</v>
       </c>
       <c r="N75">
-        <v>-159.2449152000002</v>
+        <v>-179.9742976000002</v>
       </c>
       <c r="O75">
-        <v>-31.84898304000003</v>
+        <v>-35.99485952000005</v>
       </c>
       <c r="P75">
-        <v>-127.3959321600001</v>
+        <v>-143.9794380800002</v>
       </c>
       <c r="Q75">
-        <v>119.7040678399998</v>
+        <v>103.1205619199997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1896443338631243</v>
+        <v>0.1951768082424752</v>
       </c>
       <c r="T75">
-        <v>2.22522609688239</v>
+        <v>2.310811715993251</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.1789531868106158</v>
+        <v>0.1765349005023642</v>
       </c>
       <c r="W75">
-        <v>0.09737615204426098</v>
+        <v>0.09766296080041961</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8947659340530787</v>
+        <v>0.8826745025118208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1230165611353541</v>
+        <v>0.1237445611353541</v>
       </c>
       <c r="C76">
-        <v>-1508.018707399604</v>
+        <v>-1764.973695260283</v>
       </c>
       <c r="D76">
-        <v>9754.097292600398</v>
+        <v>9671.926304739718</v>
       </c>
       <c r="E76">
-        <v>5490.116000000002</v>
+        <v>5664.900000000001</v>
       </c>
       <c r="F76">
-        <v>12934.016</v>
+        <v>13108.8</v>
       </c>
       <c r="G76">
         <v>1671.9</v>
@@ -7525,37 +7525,37 @@
         <v>1354</v>
       </c>
       <c r="M76">
-        <v>1533.9742976</v>
+        <v>1554.70368</v>
       </c>
       <c r="N76">
-        <v>-179.9742976000002</v>
+        <v>-200.7036800000003</v>
       </c>
       <c r="O76">
-        <v>-35.99485952000005</v>
+        <v>-40.14073600000006</v>
       </c>
       <c r="P76">
-        <v>-143.9794380800002</v>
+        <v>-160.5629440000002</v>
       </c>
       <c r="Q76">
-        <v>103.1205619199997</v>
+        <v>86.53705599999967</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1951768082424752</v>
+        <v>0.2011518805721742</v>
       </c>
       <c r="T76">
-        <v>2.310811715993251</v>
+        <v>2.403244184632981</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.1765349005023642</v>
+        <v>0.1741811018289993</v>
       </c>
       <c r="W76">
-        <v>0.09766296080041961</v>
+        <v>0.09794212132308068</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8826745025118208</v>
+        <v>0.8709055091449965</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1237445611353541</v>
+        <v>0.1244725611353541</v>
       </c>
       <c r="C77">
-        <v>-1764.973695260283</v>
+        <v>-2020.555790260889</v>
       </c>
       <c r="D77">
-        <v>9671.926304739718</v>
+        <v>9591.128209739112</v>
       </c>
       <c r="E77">
-        <v>5664.900000000001</v>
+        <v>5839.684000000001</v>
       </c>
       <c r="F77">
-        <v>13108.8</v>
+        <v>13283.584</v>
       </c>
       <c r="G77">
         <v>1671.9</v>
@@ -7607,37 +7607,37 @@
         <v>1354</v>
       </c>
       <c r="M77">
-        <v>1554.70368</v>
+        <v>1575.4330624</v>
       </c>
       <c r="N77">
-        <v>-200.7036800000003</v>
+        <v>-221.4330624000002</v>
       </c>
       <c r="O77">
-        <v>-40.14073600000006</v>
+        <v>-44.28661248000003</v>
       </c>
       <c r="P77">
-        <v>-160.5629440000002</v>
+        <v>-177.1464499200001</v>
       </c>
       <c r="Q77">
-        <v>86.53705599999967</v>
+        <v>69.95355007999979</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2011518805721742</v>
+        <v>0.2076248755960148</v>
       </c>
       <c r="T77">
-        <v>2.403244184632981</v>
+        <v>2.503379358992689</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.1741811018289993</v>
+        <v>0.1718892452259862</v>
       </c>
       <c r="W77">
-        <v>0.09794212132308068</v>
+        <v>0.09821393551619806</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8709055091449965</v>
+        <v>0.8594462261299308</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1244725611353541</v>
+        <v>0.1252005611353541</v>
       </c>
       <c r="C78">
-        <v>-2020.555790260889</v>
+        <v>-2274.799114290812</v>
       </c>
       <c r="D78">
-        <v>9591.128209739112</v>
+        <v>9511.66888570919</v>
       </c>
       <c r="E78">
-        <v>5839.684000000001</v>
+        <v>6014.468000000003</v>
       </c>
       <c r="F78">
-        <v>13283.584</v>
+        <v>13458.368</v>
       </c>
       <c r="G78">
         <v>1671.9</v>
@@ -7689,37 +7689,37 @@
         <v>1354</v>
       </c>
       <c r="M78">
-        <v>1575.4330624</v>
+        <v>1596.1624448</v>
       </c>
       <c r="N78">
-        <v>-221.4330624000002</v>
+        <v>-242.1624448000005</v>
       </c>
       <c r="O78">
-        <v>-44.28661248000003</v>
+        <v>-48.43248896000009</v>
       </c>
       <c r="P78">
-        <v>-177.1464499200001</v>
+        <v>-193.7299558400004</v>
       </c>
       <c r="Q78">
-        <v>69.95355007999979</v>
+        <v>53.37004415999954</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2076248755960148</v>
+        <v>0.2146607397523633</v>
       </c>
       <c r="T78">
-        <v>2.503379358992689</v>
+        <v>2.612221939818458</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.1718892452259862</v>
+        <v>0.1696569173659084</v>
       </c>
       <c r="W78">
-        <v>0.09821393551619806</v>
+        <v>0.09847868960040328</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8594462261299308</v>
+        <v>0.848284586829542</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1252005611353541</v>
+        <v>0.1259285611353541</v>
       </c>
       <c r="C79">
-        <v>-2274.799114290812</v>
+        <v>-2527.736667776129</v>
       </c>
       <c r="D79">
-        <v>9511.66888570919</v>
+        <v>9433.515332223873</v>
       </c>
       <c r="E79">
-        <v>6014.468000000003</v>
+        <v>6189.252000000002</v>
       </c>
       <c r="F79">
-        <v>13458.368</v>
+        <v>13633.152</v>
       </c>
       <c r="G79">
         <v>1671.9</v>
@@ -7771,37 +7771,37 @@
         <v>1354</v>
       </c>
       <c r="M79">
-        <v>1596.1624448</v>
+        <v>1616.8918272</v>
       </c>
       <c r="N79">
-        <v>-242.1624448000005</v>
+        <v>-262.8918272000003</v>
       </c>
       <c r="O79">
-        <v>-48.43248896000009</v>
+        <v>-52.57836544000006</v>
       </c>
       <c r="P79">
-        <v>-193.7299558400004</v>
+        <v>-210.3134617600003</v>
       </c>
       <c r="Q79">
-        <v>53.37004415999954</v>
+        <v>36.78653823999966</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2146607397523633</v>
+        <v>0.2223362279229253</v>
       </c>
       <c r="T79">
-        <v>2.612221939818458</v>
+        <v>2.730959300719297</v>
       </c>
       <c r="U79">
         <v>0.1186</v>
       </c>
       <c r="V79">
-        <v>0.1696569173659084</v>
+        <v>0.1674818286817301</v>
       </c>
       <c r="W79">
-        <v>0.09847868960040328</v>
+        <v>0.09873665511834681</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.848284586829542</v>
+        <v>0.8374091434086505</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1259285611353541</v>
+        <v>0.1266565611353541</v>
       </c>
       <c r="C80">
-        <v>-2527.736667776129</v>
+        <v>-2779.40037537721</v>
       </c>
       <c r="D80">
-        <v>9433.515332223873</v>
+        <v>9356.635624622792</v>
       </c>
       <c r="E80">
-        <v>6189.252000000002</v>
+        <v>6364.036000000002</v>
       </c>
       <c r="F80">
-        <v>13633.152</v>
+        <v>13807.936</v>
       </c>
       <c r="G80">
         <v>1671.9</v>
@@ -7853,37 +7853,37 @@
         <v>1354</v>
       </c>
       <c r="M80">
-        <v>1616.8918272</v>
+        <v>1637.6212096</v>
       </c>
       <c r="N80">
-        <v>-262.8918272000003</v>
+        <v>-283.6212096000004</v>
       </c>
       <c r="O80">
-        <v>-52.57836544000006</v>
+        <v>-56.72424192000008</v>
       </c>
       <c r="P80">
-        <v>-210.3134617600003</v>
+        <v>-226.8969676800003</v>
       </c>
       <c r="Q80">
-        <v>36.78653823999966</v>
+        <v>20.20303231999961</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2223362279229253</v>
+        <v>0.2307427149668741</v>
       </c>
       <c r="T80">
-        <v>2.730959300719297</v>
+        <v>2.86100498170593</v>
       </c>
       <c r="U80">
         <v>0.1186</v>
       </c>
       <c r="V80">
-        <v>0.1674818286817301</v>
+        <v>0.1653618055338601</v>
       </c>
       <c r="W80">
-        <v>0.09873665511834681</v>
+        <v>0.09898808986368419</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8374091434086505</v>
+        <v>0.8268090276693004</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1266565611353541</v>
+        <v>0.1273845611353541</v>
       </c>
       <c r="C81">
-        <v>-2779.40037537721</v>
+        <v>-3029.821129469823</v>
       </c>
       <c r="D81">
-        <v>9356.635624622792</v>
+        <v>9280.998870530178</v>
       </c>
       <c r="E81">
-        <v>6364.036000000002</v>
+        <v>6538.820000000002</v>
       </c>
       <c r="F81">
-        <v>13807.936</v>
+        <v>13982.72</v>
       </c>
       <c r="G81">
         <v>1671.9</v>
@@ -7935,37 +7935,37 @@
         <v>1354</v>
       </c>
       <c r="M81">
-        <v>1637.6212096</v>
+        <v>1658.350592</v>
       </c>
       <c r="N81">
-        <v>-283.6212096000004</v>
+        <v>-304.3505920000002</v>
       </c>
       <c r="O81">
-        <v>-56.72424192000008</v>
+        <v>-60.87011840000005</v>
       </c>
       <c r="P81">
-        <v>-226.8969676800003</v>
+        <v>-243.4804736000002</v>
       </c>
       <c r="Q81">
-        <v>20.20303231999961</v>
+        <v>3.619526399999728</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2307427149668741</v>
+        <v>0.2399898507152178</v>
       </c>
       <c r="T81">
-        <v>2.86100498170593</v>
+        <v>3.004055230791227</v>
       </c>
       <c r="U81">
         <v>0.1186</v>
       </c>
       <c r="V81">
-        <v>0.1653618055338601</v>
+        <v>0.1632947829646869</v>
       </c>
       <c r="W81">
-        <v>0.09898808986368419</v>
+        <v>0.09923323874038814</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8268090276693004</v>
+        <v>0.8164739148234343</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1273845611353541</v>
+        <v>0.1281125611353541</v>
       </c>
       <c r="C82">
-        <v>-3029.821129469823</v>
+        <v>-3279.02883153426</v>
       </c>
       <c r="D82">
-        <v>9280.998870530178</v>
+        <v>9206.575168465743</v>
       </c>
       <c r="E82">
-        <v>6538.820000000002</v>
+        <v>6713.604000000003</v>
       </c>
       <c r="F82">
-        <v>13982.72</v>
+        <v>14157.504</v>
       </c>
       <c r="G82">
         <v>1671.9</v>
@@ -8017,37 +8017,37 @@
         <v>1354</v>
       </c>
       <c r="M82">
-        <v>1658.350592</v>
+        <v>1679.079974400001</v>
       </c>
       <c r="N82">
-        <v>-304.3505920000002</v>
+        <v>-325.0799744000005</v>
       </c>
       <c r="O82">
-        <v>-60.87011840000005</v>
+        <v>-65.01599488000011</v>
       </c>
       <c r="P82">
-        <v>-243.4804736000002</v>
+        <v>-260.0639795200004</v>
       </c>
       <c r="Q82">
-        <v>3.619526399999728</v>
+        <v>-12.96397952000052</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2399898507152178</v>
+        <v>0.2502103691739135</v>
       </c>
       <c r="T82">
-        <v>3.004055230791227</v>
+        <v>3.162163400832871</v>
       </c>
       <c r="U82">
         <v>0.1186</v>
       </c>
       <c r="V82">
-        <v>0.1632947829646869</v>
+        <v>0.1612787979898141</v>
       </c>
       <c r="W82">
-        <v>0.09923323874038814</v>
+        <v>0.09947233455840805</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8164739148234343</v>
+        <v>0.8063939899490707</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1281125611353541</v>
+        <v>0.1986336108676528</v>
       </c>
       <c r="C83">
-        <v>-3279.02883153426</v>
+        <v>-7478.812083739746</v>
       </c>
       <c r="D83">
-        <v>9206.575168465743</v>
+        <v>5181.575916260257</v>
       </c>
       <c r="E83">
-        <v>6713.604000000003</v>
+        <v>6888.388000000003</v>
       </c>
       <c r="F83">
-        <v>14157.504</v>
+        <v>14332.288</v>
       </c>
       <c r="G83">
         <v>1671.9</v>
@@ -8099,45 +8099,45 @@
         <v>1354</v>
       </c>
       <c r="M83">
-        <v>1679.079974400001</v>
+        <v>2877.923430400001</v>
       </c>
       <c r="N83">
-        <v>-325.0799744000005</v>
+        <v>-1523.923430400001</v>
       </c>
       <c r="O83">
-        <v>-65.01599488000011</v>
+        <v>-304.7846860800001</v>
       </c>
       <c r="P83">
-        <v>-260.0639795200004</v>
+        <v>-1219.138744320001</v>
       </c>
       <c r="Q83">
-        <v>-12.96397952000052</v>
+        <v>-972.0387443200007</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2502103691739135</v>
+        <v>0.274838999307457</v>
       </c>
       <c r="T83">
-        <v>3.162163400832871</v>
+        <v>3.543160476155798</v>
       </c>
       <c r="U83">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1612787979898141</v>
+        <v>0.09409562364984871</v>
       </c>
       <c r="W83">
-        <v>0.09947233455840805</v>
+        <v>0.1819055987711104</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8063939899490707</v>
+        <v>0.4704781182492435</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1986336108676528</v>
+        <v>0.2001836108676528</v>
       </c>
       <c r="C84">
-        <v>-7478.812083739746</v>
+        <v>-7702.912244476147</v>
       </c>
       <c r="D84">
-        <v>5181.575916260257</v>
+        <v>5132.259755523854</v>
       </c>
       <c r="E84">
-        <v>6888.388000000003</v>
+        <v>7063.172000000002</v>
       </c>
       <c r="F84">
-        <v>14332.288</v>
+        <v>14507.072</v>
       </c>
       <c r="G84">
         <v>1671.9</v>
@@ -8181,37 +8181,37 @@
         <v>1354</v>
       </c>
       <c r="M84">
-        <v>2877.923430400001</v>
+        <v>2913.020057600001</v>
       </c>
       <c r="N84">
-        <v>-1523.923430400001</v>
+        <v>-1559.020057600001</v>
       </c>
       <c r="O84">
-        <v>-304.7846860800001</v>
+        <v>-311.8040115200001</v>
       </c>
       <c r="P84">
-        <v>-1219.138744320001</v>
+        <v>-1247.216046080001</v>
       </c>
       <c r="Q84">
-        <v>-972.0387443200007</v>
+        <v>-1000.116046080001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.274838999307457</v>
+        <v>0.2883118816196603</v>
       </c>
       <c r="T84">
-        <v>3.543160476155798</v>
+        <v>3.75158168063555</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09409562364984871</v>
+        <v>0.09296194143719994</v>
       </c>
       <c r="W84">
-        <v>0.1819055987711104</v>
+        <v>0.1821332421594103</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4704781182492435</v>
+        <v>0.4648097071859996</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2001836108676528</v>
+        <v>0.2017336108676528</v>
       </c>
       <c r="C85">
-        <v>-7702.912244476147</v>
+        <v>-7926.082512691743</v>
       </c>
       <c r="D85">
-        <v>5132.259755523854</v>
+        <v>5083.87348730826</v>
       </c>
       <c r="E85">
-        <v>7063.172000000002</v>
+        <v>7237.956000000004</v>
       </c>
       <c r="F85">
-        <v>14507.072</v>
+        <v>14681.856</v>
       </c>
       <c r="G85">
         <v>1671.9</v>
@@ -8263,37 +8263,37 @@
         <v>1354</v>
       </c>
       <c r="M85">
-        <v>2913.020057600001</v>
+        <v>2948.116684800001</v>
       </c>
       <c r="N85">
-        <v>-1559.020057600001</v>
+        <v>-1594.116684800001</v>
       </c>
       <c r="O85">
-        <v>-311.8040115200001</v>
+        <v>-318.8233369600002</v>
       </c>
       <c r="P85">
-        <v>-1247.216046080001</v>
+        <v>-1275.29334784</v>
       </c>
       <c r="Q85">
-        <v>-1000.116046080001</v>
+        <v>-1028.193347840001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2883118816196603</v>
+        <v>0.3034688742208891</v>
       </c>
       <c r="T85">
-        <v>3.75158168063555</v>
+        <v>3.986055535675273</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09296194143719994</v>
+        <v>0.09185525165818564</v>
       </c>
       <c r="W85">
-        <v>0.1821332421594103</v>
+        <v>0.1823554654670363</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4648097071859996</v>
+        <v>0.4592762582909282</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2017336108676528</v>
+        <v>0.2032836108676528</v>
       </c>
       <c r="C86">
-        <v>-7926.082512691741</v>
+        <v>-8148.348943454976</v>
       </c>
       <c r="D86">
-        <v>5083.87348730826</v>
+        <v>5036.391056545025</v>
       </c>
       <c r="E86">
-        <v>7237.956000000002</v>
+        <v>7412.740000000002</v>
       </c>
       <c r="F86">
-        <v>14681.856</v>
+        <v>14856.64</v>
       </c>
       <c r="G86">
         <v>1671.9</v>
@@ -8345,37 +8345,37 @@
         <v>1354</v>
       </c>
       <c r="M86">
-        <v>2948.1166848</v>
+        <v>2983.213312</v>
       </c>
       <c r="N86">
-        <v>-1594.1166848</v>
+        <v>-1629.213312</v>
       </c>
       <c r="O86">
-        <v>-318.8233369600001</v>
+        <v>-325.8426624000001</v>
       </c>
       <c r="P86">
-        <v>-1275.29334784</v>
+        <v>-1303.3706496</v>
       </c>
       <c r="Q86">
-        <v>-1028.19334784</v>
+        <v>-1056.2706496</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.303468874220889</v>
+        <v>0.3206467991689483</v>
       </c>
       <c r="T86">
-        <v>3.98605553567527</v>
+        <v>4.251792571386956</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09185525165818564</v>
+        <v>0.09077460163867758</v>
       </c>
       <c r="W86">
-        <v>0.1823554654670363</v>
+        <v>0.1825724599909536</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4592762582909282</v>
+        <v>0.4538730081933879</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2032836108676528</v>
+        <v>0.2048336108676528</v>
       </c>
       <c r="C87">
-        <v>-8148.348943454976</v>
+        <v>-8369.736627443603</v>
       </c>
       <c r="D87">
-        <v>5036.391056545025</v>
+        <v>4989.787372556398</v>
       </c>
       <c r="E87">
-        <v>7412.740000000002</v>
+        <v>7587.524000000001</v>
       </c>
       <c r="F87">
-        <v>14856.64</v>
+        <v>15031.424</v>
       </c>
       <c r="G87">
         <v>1671.9</v>
@@ -8427,37 +8427,37 @@
         <v>1354</v>
       </c>
       <c r="M87">
-        <v>2983.213312</v>
+        <v>3018.3099392</v>
       </c>
       <c r="N87">
-        <v>-1629.213312</v>
+        <v>-1664.3099392</v>
       </c>
       <c r="O87">
-        <v>-325.8426624000001</v>
+        <v>-332.8619878400001</v>
       </c>
       <c r="P87">
-        <v>-1303.3706496</v>
+        <v>-1331.44795136</v>
       </c>
       <c r="Q87">
-        <v>-1056.2706496</v>
+        <v>-1084.34795136</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3206467991689483</v>
+        <v>0.3402787133953017</v>
       </c>
       <c r="T87">
-        <v>4.251792571386956</v>
+        <v>4.555492040771738</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09077460163867758</v>
+        <v>0.08971908301497203</v>
       </c>
       <c r="W87">
-        <v>0.1825724599909536</v>
+        <v>0.1827844081305936</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4538730081933879</v>
+        <v>0.4485954150748601</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2048336108676528</v>
+        <v>0.2063836108676528</v>
       </c>
       <c r="C88">
-        <v>-8369.736627443603</v>
+        <v>-8590.269735154985</v>
       </c>
       <c r="D88">
-        <v>4989.787372556398</v>
+        <v>4944.038264845015</v>
       </c>
       <c r="E88">
-        <v>7587.524000000001</v>
+        <v>7762.308000000001</v>
       </c>
       <c r="F88">
-        <v>15031.424</v>
+        <v>15206.208</v>
       </c>
       <c r="G88">
         <v>1671.9</v>
@@ -8509,37 +8509,37 @@
         <v>1354</v>
       </c>
       <c r="M88">
-        <v>3018.3099392</v>
+        <v>3053.4065664</v>
       </c>
       <c r="N88">
-        <v>-1664.3099392</v>
+        <v>-1699.4065664</v>
       </c>
       <c r="O88">
-        <v>-332.8619878400001</v>
+        <v>-339.8813132800001</v>
       </c>
       <c r="P88">
-        <v>-1331.44795136</v>
+        <v>-1359.52525312</v>
       </c>
       <c r="Q88">
-        <v>-1084.34795136</v>
+        <v>-1112.42525312</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3402787133953017</v>
+        <v>0.3629309221180172</v>
       </c>
       <c r="T88">
-        <v>4.555492040771738</v>
+        <v>4.905914505446487</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08971908301497203</v>
+        <v>0.08868782918721374</v>
       </c>
       <c r="W88">
-        <v>0.1827844081305936</v>
+        <v>0.1829914838992075</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4485954150748601</v>
+        <v>0.4434391459360686</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2063836108676528</v>
+        <v>0.2079336108676528</v>
       </c>
       <c r="C89">
-        <v>-8590.269735154985</v>
+        <v>-8809.971558706442</v>
       </c>
       <c r="D89">
-        <v>4944.038264845015</v>
+        <v>4899.120441293559</v>
       </c>
       <c r="E89">
-        <v>7762.308000000001</v>
+        <v>7937.092000000002</v>
       </c>
       <c r="F89">
-        <v>15206.208</v>
+        <v>15380.992</v>
       </c>
       <c r="G89">
         <v>1671.9</v>
@@ -8591,37 +8591,37 @@
         <v>1354</v>
       </c>
       <c r="M89">
-        <v>3053.4065664</v>
+        <v>3088.5031936</v>
       </c>
       <c r="N89">
-        <v>-1699.4065664</v>
+        <v>-1734.5031936</v>
       </c>
       <c r="O89">
-        <v>-339.8813132800001</v>
+        <v>-346.9006387200001</v>
       </c>
       <c r="P89">
-        <v>-1359.52525312</v>
+        <v>-1387.60255488</v>
       </c>
       <c r="Q89">
-        <v>-1112.42525312</v>
+        <v>-1140.50255488</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3629309221180172</v>
+        <v>0.3893584989611854</v>
       </c>
       <c r="T89">
-        <v>4.905914505446487</v>
+        <v>5.314740714233695</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08868782918721374</v>
+        <v>0.08768001294644993</v>
       </c>
       <c r="W89">
-        <v>0.1829914838992075</v>
+        <v>0.1831938534003529</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4434391459360686</v>
+        <v>0.4384000647322497</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2079336108676528</v>
+        <v>0.2094836108676527</v>
       </c>
       <c r="C90">
-        <v>-8809.971558706442</v>
+        <v>-9028.864551377512</v>
       </c>
       <c r="D90">
-        <v>4899.120441293559</v>
+        <v>4855.01144862249</v>
       </c>
       <c r="E90">
-        <v>7937.092000000002</v>
+        <v>8111.876000000002</v>
       </c>
       <c r="F90">
-        <v>15380.992</v>
+        <v>15555.776</v>
       </c>
       <c r="G90">
         <v>1671.9</v>
@@ -8673,37 +8673,37 @@
         <v>1354</v>
       </c>
       <c r="M90">
-        <v>3088.5031936</v>
+        <v>3123.599820800001</v>
       </c>
       <c r="N90">
-        <v>-1734.5031936</v>
+        <v>-1769.599820800001</v>
       </c>
       <c r="O90">
-        <v>-346.9006387200001</v>
+        <v>-353.9199641600001</v>
       </c>
       <c r="P90">
-        <v>-1387.60255488</v>
+        <v>-1415.67985664</v>
       </c>
       <c r="Q90">
-        <v>-1140.50255488</v>
+        <v>-1168.579856640001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3893584989611854</v>
+        <v>0.4205910897758386</v>
       </c>
       <c r="T90">
-        <v>5.314740714233695</v>
+        <v>5.797898960982212</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08768001294644993</v>
+        <v>0.08669484426165835</v>
       </c>
       <c r="W90">
-        <v>0.1831938534003529</v>
+        <v>0.183391675272259</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4384000647322497</v>
+        <v>0.4334742213082918</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2094836108676527</v>
+        <v>0.2110336108676528</v>
       </c>
       <c r="C91">
-        <v>-9028.864551377512</v>
+        <v>-9246.97036503516</v>
       </c>
       <c r="D91">
-        <v>4855.01144862249</v>
+        <v>4811.68963496484</v>
       </c>
       <c r="E91">
-        <v>8111.876000000002</v>
+        <v>8286.660000000002</v>
       </c>
       <c r="F91">
-        <v>15555.776</v>
+        <v>15730.56</v>
       </c>
       <c r="G91">
         <v>1671.9</v>
@@ -8755,37 +8755,37 @@
         <v>1354</v>
       </c>
       <c r="M91">
-        <v>3123.599820800001</v>
+        <v>3158.696448</v>
       </c>
       <c r="N91">
-        <v>-1769.599820800001</v>
+        <v>-1804.696448</v>
       </c>
       <c r="O91">
-        <v>-353.9199641600001</v>
+        <v>-360.9392896000001</v>
       </c>
       <c r="P91">
-        <v>-1415.67985664</v>
+        <v>-1443.7571584</v>
       </c>
       <c r="Q91">
-        <v>-1168.579856640001</v>
+        <v>-1196.6571584</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4205910897758386</v>
+        <v>0.4580701987534225</v>
       </c>
       <c r="T91">
-        <v>5.797898960982212</v>
+        <v>6.377688857080434</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08669484426165835</v>
+        <v>0.08573156821430661</v>
       </c>
       <c r="W91">
-        <v>0.183391675272259</v>
+        <v>0.1835851011025672</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4334742213082918</v>
+        <v>0.428657841071533</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2110336108676528</v>
+        <v>0.2125836108676528</v>
       </c>
       <c r="C92">
-        <v>-9246.97036503516</v>
+        <v>-9464.309885573053</v>
       </c>
       <c r="D92">
-        <v>4811.68963496484</v>
+        <v>4769.134114426948</v>
       </c>
       <c r="E92">
-        <v>8286.660000000002</v>
+        <v>8461.444000000001</v>
       </c>
       <c r="F92">
-        <v>15730.56</v>
+        <v>15905.344</v>
       </c>
       <c r="G92">
         <v>1671.9</v>
@@ -8837,37 +8837,37 @@
         <v>1354</v>
       </c>
       <c r="M92">
-        <v>3158.696448</v>
+        <v>3193.7930752</v>
       </c>
       <c r="N92">
-        <v>-1804.696448</v>
+        <v>-1839.7930752</v>
       </c>
       <c r="O92">
-        <v>-360.9392896000001</v>
+        <v>-367.95861504</v>
       </c>
       <c r="P92">
-        <v>-1443.7571584</v>
+        <v>-1471.83446016</v>
       </c>
       <c r="Q92">
-        <v>-1196.6571584</v>
+        <v>-1224.73446016</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4580701987534225</v>
+        <v>0.503877998614914</v>
       </c>
       <c r="T92">
-        <v>6.377688857080434</v>
+        <v>7.086320952311596</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08573156821430661</v>
+        <v>0.08478946306909446</v>
       </c>
       <c r="W92">
-        <v>0.1835851011025672</v>
+        <v>0.1837742758157259</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.428657841071533</v>
+        <v>0.4239473153454723</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2125836108676528</v>
+        <v>0.2141336108676528</v>
       </c>
       <c r="C93">
-        <v>-9464.309885573053</v>
+        <v>-9680.903266486665</v>
       </c>
       <c r="D93">
-        <v>4769.134114426948</v>
+        <v>4727.324733513337</v>
       </c>
       <c r="E93">
-        <v>8461.444000000001</v>
+        <v>8636.228000000003</v>
       </c>
       <c r="F93">
-        <v>15905.344</v>
+        <v>16080.128</v>
       </c>
       <c r="G93">
         <v>1671.9</v>
@@ -8919,37 +8919,37 @@
         <v>1354</v>
       </c>
       <c r="M93">
-        <v>3193.7930752</v>
+        <v>3228.889702400001</v>
       </c>
       <c r="N93">
-        <v>-1839.7930752</v>
+        <v>-1874.889702400001</v>
       </c>
       <c r="O93">
-        <v>-367.95861504</v>
+        <v>-374.9779404800001</v>
       </c>
       <c r="P93">
-        <v>-1471.83446016</v>
+        <v>-1499.911761920001</v>
       </c>
       <c r="Q93">
-        <v>-1224.73446016</v>
+        <v>-1252.811761920001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.503877998614914</v>
+        <v>0.5611377484417782</v>
       </c>
       <c r="T93">
-        <v>7.086320952311596</v>
+        <v>7.972111071350546</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08478946306909446</v>
+        <v>0.08386783847051732</v>
       </c>
       <c r="W93">
-        <v>0.1837742758157259</v>
+        <v>0.1839593380351201</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4239473153454723</v>
+        <v>0.4193391923525867</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2141336108676528</v>
+        <v>0.2156836108676528</v>
       </c>
       <c r="C94">
-        <v>-9680.903266486665</v>
+        <v>-9896.769960697729</v>
       </c>
       <c r="D94">
-        <v>4727.324733513337</v>
+        <v>4686.242039302273</v>
       </c>
       <c r="E94">
-        <v>8636.228000000003</v>
+        <v>8811.012000000002</v>
       </c>
       <c r="F94">
-        <v>16080.128</v>
+        <v>16254.912</v>
       </c>
       <c r="G94">
         <v>1671.9</v>
@@ -9001,37 +9001,37 @@
         <v>1354</v>
       </c>
       <c r="M94">
-        <v>3228.889702400001</v>
+        <v>3263.9863296</v>
       </c>
       <c r="N94">
-        <v>-1874.889702400001</v>
+        <v>-1909.9863296</v>
       </c>
       <c r="O94">
-        <v>-374.9779404800001</v>
+        <v>-381.9972659200001</v>
       </c>
       <c r="P94">
-        <v>-1499.911761920001</v>
+        <v>-1527.98906368</v>
       </c>
       <c r="Q94">
-        <v>-1252.811761920001</v>
+        <v>-1280.88906368</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5611377484417782</v>
+        <v>0.6347574267906038</v>
       </c>
       <c r="T94">
-        <v>7.972111071350546</v>
+        <v>9.110984081543481</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08386783847051732</v>
+        <v>0.0829660337557806</v>
       </c>
       <c r="W94">
-        <v>0.1839593380351201</v>
+        <v>0.1841404204218393</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4193391923525867</v>
+        <v>0.4148301687789029</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2156836108676528</v>
+        <v>0.2172336108676527</v>
       </c>
       <c r="C95">
-        <v>-9896.769960697729</v>
+        <v>-10111.92875073357</v>
       </c>
       <c r="D95">
-        <v>4686.242039302273</v>
+        <v>4645.867249266436</v>
       </c>
       <c r="E95">
-        <v>8811.012000000002</v>
+        <v>8985.796000000004</v>
       </c>
       <c r="F95">
-        <v>16254.912</v>
+        <v>16429.696</v>
       </c>
       <c r="G95">
         <v>1671.9</v>
@@ -9083,37 +9083,37 @@
         <v>1354</v>
       </c>
       <c r="M95">
-        <v>3263.9863296</v>
+        <v>3299.082956800001</v>
       </c>
       <c r="N95">
-        <v>-1909.9863296</v>
+        <v>-1945.082956800001</v>
       </c>
       <c r="O95">
-        <v>-381.9972659200001</v>
+        <v>-389.0165913600002</v>
       </c>
       <c r="P95">
-        <v>-1527.98906368</v>
+        <v>-1556.066365440001</v>
       </c>
       <c r="Q95">
-        <v>-1280.88906368</v>
+        <v>-1308.966365440001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6347574267906038</v>
+        <v>0.7329169979223713</v>
       </c>
       <c r="T95">
-        <v>9.110984081543481</v>
+        <v>10.6294814284674</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0829660337557806</v>
+        <v>0.08208341637539994</v>
       </c>
       <c r="W95">
-        <v>0.1841404204218393</v>
+        <v>0.1843176499918197</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4148301687789029</v>
+        <v>0.4104170818769997</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2172336108676527</v>
+        <v>0.2187836108676528</v>
       </c>
       <c r="C96">
-        <v>-10111.92875073357</v>
+        <v>-10326.39777735963</v>
       </c>
       <c r="D96">
-        <v>4645.867249266436</v>
+        <v>4606.182222640368</v>
       </c>
       <c r="E96">
-        <v>8985.796000000004</v>
+        <v>9160.580000000004</v>
       </c>
       <c r="F96">
-        <v>16429.696</v>
+        <v>16604.48</v>
       </c>
       <c r="G96">
         <v>1671.9</v>
@@ -9165,37 +9165,37 @@
         <v>1354</v>
       </c>
       <c r="M96">
-        <v>3299.082956800001</v>
+        <v>3334.179584000001</v>
       </c>
       <c r="N96">
-        <v>-1945.082956800001</v>
+        <v>-1980.179584000001</v>
       </c>
       <c r="O96">
-        <v>-389.0165913600002</v>
+        <v>-396.0359168000002</v>
       </c>
       <c r="P96">
-        <v>-1556.066365440001</v>
+        <v>-1584.143667200001</v>
       </c>
       <c r="Q96">
-        <v>-1308.966365440001</v>
+        <v>-1337.043667200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7329169979223713</v>
+        <v>0.870340397506846</v>
       </c>
       <c r="T96">
-        <v>10.6294814284674</v>
+        <v>12.75537771416088</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08208341637539994</v>
+        <v>0.08121938041355362</v>
       </c>
       <c r="W96">
-        <v>0.1843176499918197</v>
+        <v>0.1844911484129584</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4104170818769997</v>
+        <v>0.4060969020677681</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2187836108676528</v>
+        <v>0.2203336108676528</v>
       </c>
       <c r="C97">
-        <v>-10326.39777735963</v>
+        <v>-10540.19456675705</v>
       </c>
       <c r="D97">
-        <v>4606.182222640368</v>
+        <v>4567.169433242948</v>
       </c>
       <c r="E97">
-        <v>9160.580000000004</v>
+        <v>9335.364000000003</v>
       </c>
       <c r="F97">
-        <v>16604.48</v>
+        <v>16779.264</v>
       </c>
       <c r="G97">
         <v>1671.9</v>
@@ -9247,37 +9247,37 @@
         <v>1354</v>
       </c>
       <c r="M97">
-        <v>3334.179584000001</v>
+        <v>3369.2762112</v>
       </c>
       <c r="N97">
-        <v>-1980.179584000001</v>
+        <v>-2015.2762112</v>
       </c>
       <c r="O97">
-        <v>-396.0359168000002</v>
+        <v>-403.0552422400001</v>
       </c>
       <c r="P97">
-        <v>-1584.143667200001</v>
+        <v>-1612.22096896</v>
       </c>
       <c r="Q97">
-        <v>-1337.043667200001</v>
+        <v>-1365.12096896</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.870340397506846</v>
+        <v>1.076475496883558</v>
       </c>
       <c r="T97">
-        <v>12.75537771416088</v>
+        <v>15.94422214270111</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08121938041355362</v>
+        <v>0.08037334520091244</v>
       </c>
       <c r="W97">
-        <v>0.1844911484129584</v>
+        <v>0.1846610322836568</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4060969020677681</v>
+        <v>0.4018667260045622</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2203336108676528</v>
+        <v>0.2218836108676527</v>
       </c>
       <c r="C98">
-        <v>-10540.19456675705</v>
+        <v>-10753.33605633063</v>
       </c>
       <c r="D98">
-        <v>4567.169433242947</v>
+        <v>4528.811943669378</v>
       </c>
       <c r="E98">
-        <v>9335.364</v>
+        <v>9510.148000000003</v>
       </c>
       <c r="F98">
-        <v>16779.264</v>
+        <v>16954.048</v>
       </c>
       <c r="G98">
         <v>1671.9</v>
@@ -9329,37 +9329,37 @@
         <v>1354</v>
       </c>
       <c r="M98">
-        <v>3369.2762112</v>
+        <v>3404.372838400001</v>
       </c>
       <c r="N98">
-        <v>-2015.2762112</v>
+        <v>-2050.372838400001</v>
       </c>
       <c r="O98">
-        <v>-403.05524224</v>
+        <v>-410.0745676800001</v>
       </c>
       <c r="P98">
-        <v>-1612.22096896</v>
+        <v>-1640.29827072</v>
       </c>
       <c r="Q98">
-        <v>-1365.12096896</v>
+        <v>-1393.19827072</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.076475496883555</v>
+        <v>1.42003399584474</v>
       </c>
       <c r="T98">
-        <v>15.94422214270107</v>
+        <v>21.25896285693476</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08037334520091245</v>
+        <v>0.07954475401327417</v>
       </c>
       <c r="W98">
-        <v>0.1846610322836568</v>
+        <v>0.1848274133941346</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4018667260045622</v>
+        <v>0.3977237700663708</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2218836108676527</v>
+        <v>0.2234336108676528</v>
       </c>
       <c r="C99">
-        <v>-10753.33605633063</v>
+        <v>-10965.83861922717</v>
       </c>
       <c r="D99">
-        <v>4528.811943669378</v>
+        <v>4491.093380772835</v>
       </c>
       <c r="E99">
-        <v>9510.148000000003</v>
+        <v>9684.932000000003</v>
       </c>
       <c r="F99">
-        <v>16954.048</v>
+        <v>17128.832</v>
       </c>
       <c r="G99">
         <v>1671.9</v>
@@ -9411,37 +9411,37 @@
         <v>1354</v>
       </c>
       <c r="M99">
-        <v>3404.372838400001</v>
+        <v>3439.469465600001</v>
       </c>
       <c r="N99">
-        <v>-2050.372838400001</v>
+        <v>-2085.469465600001</v>
       </c>
       <c r="O99">
-        <v>-410.0745676800001</v>
+        <v>-417.0938931200001</v>
       </c>
       <c r="P99">
-        <v>-1640.29827072</v>
+        <v>-1668.375572480001</v>
       </c>
       <c r="Q99">
-        <v>-1393.19827072</v>
+        <v>-1421.275572480001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.42003399584474</v>
+        <v>2.10715099376711</v>
       </c>
       <c r="T99">
-        <v>21.25896285693476</v>
+        <v>31.88844428540214</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07954475401327417</v>
+        <v>0.07873307284987341</v>
       </c>
       <c r="W99">
-        <v>0.1848274133941346</v>
+        <v>0.1849903989717454</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3977237700663708</v>
+        <v>0.393665364249367</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2234336108676528</v>
+        <v>0.2249836108676527</v>
       </c>
       <c r="C100">
-        <v>-10965.83861922717</v>
+        <v>-11177.71808763876</v>
       </c>
       <c r="D100">
-        <v>4491.093380772835</v>
+        <v>4453.997912361241</v>
       </c>
       <c r="E100">
-        <v>9684.932000000003</v>
+        <v>9859.716000000002</v>
       </c>
       <c r="F100">
-        <v>17128.832</v>
+        <v>17303.616</v>
       </c>
       <c r="G100">
         <v>1671.9</v>
@@ -9493,37 +9493,37 @@
         <v>1354</v>
       </c>
       <c r="M100">
-        <v>3439.469465600001</v>
+        <v>3474.566092800001</v>
       </c>
       <c r="N100">
-        <v>-2085.469465600001</v>
+        <v>-2120.566092800001</v>
       </c>
       <c r="O100">
-        <v>-417.0938931200001</v>
+        <v>-424.1132185600002</v>
       </c>
       <c r="P100">
-        <v>-1668.375572480001</v>
+        <v>-1696.45287424</v>
       </c>
       <c r="Q100">
-        <v>-1421.275572480001</v>
+        <v>-1449.352874240001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.10715099376711</v>
+        <v>4.168501987534221</v>
       </c>
       <c r="T100">
-        <v>31.88844428540214</v>
+        <v>63.77688857080427</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07873307284987341</v>
+        <v>0.07793778928573328</v>
       </c>
       <c r="W100">
-        <v>0.1849903989717454</v>
+        <v>0.1851500919114248</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.393665364249367</v>
+        <v>0.3896889464286664</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2249836108676527</v>
-      </c>
-      <c r="C101">
-        <v>-11177.71808763876</v>
-      </c>
-      <c r="D101">
-        <v>4453.997912361241</v>
-      </c>
-      <c r="E101">
-        <v>9859.716000000002</v>
-      </c>
-      <c r="F101">
-        <v>17303.616</v>
-      </c>
-      <c r="G101">
-        <v>1671.9</v>
-      </c>
-      <c r="H101">
-        <v>10034.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1601.1</v>
-      </c>
-      <c r="K101">
-        <v>247.0999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1354</v>
-      </c>
-      <c r="M101">
-        <v>3474.566092800001</v>
-      </c>
-      <c r="N101">
-        <v>-2120.566092800001</v>
-      </c>
-      <c r="O101">
-        <v>-424.1132185600002</v>
-      </c>
-      <c r="P101">
-        <v>-1696.45287424</v>
-      </c>
-      <c r="Q101">
-        <v>-1449.352874240001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.168501987534221</v>
-      </c>
-      <c r="T101">
-        <v>63.77688857080427</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07793778928573328</v>
-      </c>
-      <c r="W101">
-        <v>0.1851500919114248</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3896889464286664</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
